--- a/input/mapping/008. OCB_GOLD_TCKH_V_CUST_STATUS_BAOANH.xlsx
+++ b/input/mapping/008. OCB_GOLD_TCKH_V_CUST_STATUS_BAOANH.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/ANHPB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="352" documentId="13_ncr:1_{B6C0F684-96C5-4E16-9696-74D396B07D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F500C63-678E-4CCF-BAEC-7C699D27486C}"/>
+  <xr:revisionPtr revIDLastSave="406" documentId="13_ncr:1_{B6C0F684-96C5-4E16-9696-74D396B07D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD51B7AC-B97F-4FEE-BA11-E91ECF4FEA9D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{15579902-C16A-4DCC-801B-11A268672AD5}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="350">
   <si>
     <t>V_CUST_STATUS  —  Data Lineage Mind Map</t>
   </si>
@@ -265,33 +265,49 @@
   <si>
     <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
--- Ngày ETL nhận từ param :DATADT (job truyền vào, định dạng yyyyMMdd).
--- Dùng to_date(:DATADT, 'yyyyMMdd') inline ở mọi chỗ.
--- Daily snapshot trên Liquid Clustering: REPLACE WHERE chỉ thay thế đúng
--- lát cắt DATA_DT của ngày ETL (atomic, idempotent khi re-run cùng ngày),
+CREATE TABLE IF NOT EXISTS CST_LCS_KT_30D_FINAL_CASE5 (
+    DATA_DT                 DATE,
+    CIF                     DECIMAL(10,0),
+    T_COMPANY_BOOK          STRING,
+    T_CREATE_DATE           DATE NOT NULL,
+    FINAL_STATUS            STRING,
+    SCTR                    DECIMAL(10,0),
+    T_DESCRIPTION           STRING,
+    CST_GRP                 STRING,
+    CUST_GROUP_NAME         STRING,
+    CUST_GROUP_LINE         STRING,
+    CUST_GROUP_LINE_SHORT   STRING,
+    TIENGUI                 DECIMAL(20,4),
+    TIENVAY                 DECIMAL(20,4),
+    CUST_CURRENT_ACCT_A1    DECIMAL(20,4),
+    CIF_LOANCLASS            DECIMAL(3,0),
+    DOANHSO_BAOLANH_30D     DECIMAL(31,4),
+    DOANHSO_LC_30D          DECIMAL(31,4),
+    NUM_TRANS               INT,
+    ACTIVE_INDEX            INT,
+    T24_STATUS              STRING,
+    T24_ACTIVE_RB           INT,
+    T24_ACTIVE_COMB         INT,
+    T24_ACTIVE_TRE          INT,
+    T24_ACTIVE_CIB          INT,
+    T24_ACTIVE_CMB          INT,
+    T24_ACTIVE_DCTC         INT,
+    T24_ACTIVE_LIO          INT,
+    W4_STATUS               STRING,
+    W4_ACTIVE_RB            INT,
+    W4_ACTIVE_LIO           INT,
+    DATE_SYS                TIMESTAMP
+)
+USING DELTA;
 INSERT INTO CST_LCS_KT_30D_FINAL_CASE5
 REPLACE WHERE DATA_DT = to_date(:DATADT, 'yyyyMMdd')
 WITH
--- =========================================================================
--- STS_DEL / ACTIVE theo template chuẩn: &lt;ent&gt;_sts_del chỉ chứa hashkey có
--- trạng thái mới nhất (&lt;= DATADT) = 'D'; &lt;ent&gt;_active = Hub LEFT JOIN
--- &lt;ent&gt;_sts_del rồi loại các hashkey khớp (WHERE ... IS NULL). Đúng chuẩn
--- Data Vault: (1) delete phát sinh SAU DATADT không ảnh hưởng snapshot quá
--- khứ; (2) key bị xóa rồi tái tạo (D -&gt; I/U &lt;= DATADT) KHÔNG bị loại nhầm.
--- =========================================================================
 cte_customer_sts_del AS (
     SELECT customer_hashkey
     FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_customer')
     WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY customer_hashkey
     HAVING max_by(cdc_status, source_event_date) = 'D'
-),
-cte_customer_active AS (
-    SELECT h.customer_hashkey, h.business_key, h.source_event_date
-    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_customer') h
-    LEFT JOIN cte_customer_sts_del d ON d.customer_hashkey = h.customer_hashkey
-    WHERE h.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
-      AND d.customer_hashkey IS NULL
 ),
 cte_account_sts_del AS (
     SELECT account_hashkey
@@ -314,11 +330,68 @@
     GROUP BY md_deal_hashkey
     HAVING max_by(cdc_status, source_event_date) = 'D'
 ),
--- =========================================================================
--- 0. TRỤC CHÍNH: hub_customer, loại customer đã bị xóa (cte_customer_sts_del
---    qua cte_customer_active). Dedup theo customer_hashkey (giá trị max_by
---    theo source_event_date lớn nhất, giữ nguyên như bản gốc).
--- =========================================================================
+-- ===== Rule 2.12: snapshot mỗi bảng Silver đọc nhiều nơi thành 1 CTE duy nhất =====
+cte_snap_hub_customer AS (
+    SELECT customer_hashkey, business_key, source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_customer')
+),
+cte_customer_active AS (
+    SELECT h.customer_hashkey, h.business_key, h.source_event_date
+    FROM cte_snap_hub_customer h
+    LEFT JOIN cte_customer_sts_del d ON d.customer_hashkey = h.customer_hashkey
+    WHERE h.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+      AND d.customer_hashkey IS NULL
+),
+cte_snap_hub_branch AS (
+    SELECT branch_hashkey, business_key
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_branch')
+),
+cte_snap_hub_account AS (
+    SELECT account_hashkey, business_key
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_account')
+),
+cte_snap_link_account_customer AS (
+    SELECT customer_hashkey, account_hashkey, source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.link_account_customer')
+),
+cte_snap_link_crb_account AS (
+    SELECT account_hashkey, crb_hashkey, source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.link_crb_account')
+),
+cte_snap_hub_crb AS (
+    SELECT crb_hashkey, gl, tieukhoan
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_crb')
+),
+cte_snap_link_letter_of_credit_customer AS (
+    SELECT customer_hashkey, letter_of_credit_hashkey, source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.link_letter_of_credit_customer')
+),
+cte_snap_sat_account_balance AS (
+    SELECT account_hashkey, t_open_actual_bal, t_currency, source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_account_balance')
+    WHERE source_event_date = to_date(:DATADT, 'yyyyMMdd')
+),
+-- ===== Rule X.1: rút link về current (1 dòng / driving key) trước khi join, chống fan-out =====
+cte_link_crb_account_cur AS (
+    SELECT
+        account_hashkey,
+        max_by(crb_hashkey, source_event_date) AS crb_hashkey
+    FROM cte_snap_link_crb_account
+    WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY account_hashkey
+),
+cte_link_md_deal_customer_cur AS (
+    SELECT
+        md_deal_hashkey,
+        max_by(customer_hashkey, source_event_date) AS customer_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.link_md_deal_customer')
+    WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY md_deal_hashkey
+),
+cte_snap_calendar AS (
+    SELECT msr_prd_id, bsn_day_f
+    FROM IDENTIFIER(:cleaned || '.business_vault.calendar')
+),
 base_customer AS (
     SELECT
         h.customer_hashkey,
@@ -327,24 +400,16 @@
     FROM cte_customer_active h
     GROUP BY h.customer_hashkey
 ),
--- =========================================================================
--- 3. T_COMPANY_BOOK: link_customer_branch -&gt; hub_branch.business_key
---    Dedup theo customer_hashkey (giữ branch mới nhất) bằng MAX_BY.
--- =========================================================================
 cte_company_book AS (
     SELECT
         lcb.customer_hashkey,
         max_by(hb.business_key, lcb.source_event_date) AS t_company_book
     FROM IDENTIFIER(:cleaned || '.raw_vault.link_customer_branch') lcb
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_branch') hb
+    JOIN cte_snap_hub_branch hb
       ON hb.branch_hashkey = lcb.branch_hashkey
+    WHERE lcb.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY lcb.customer_hashkey
 ),
--- =========================================================================
--- 4. T_CREATE_DATE: NVL(sat_customer_information.T_CREATE_DATE,
---                       hub_customer.source_event_date)
---    Lọc sat: max(source_event_date) &lt;= [ETL]. Dedup theo customer_hashkey.
--- =========================================================================
 cte_create_date AS (
     SELECT
         sci.customer_hashkey,
@@ -353,11 +418,6 @@
     WHERE sci.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY sci.customer_hashkey
 ),
--- =========================================================================
--- 6,8,15. sat_customer_classification: SCTR, CST_GRP, CIF_LOANCLASS
---    Gộp chung vì cùng 1 satellite, cùng điều kiện lọc/dedup.
---    Lọc sat: max(source_event_date) &lt;= [ETL]. Dedup theo customer_hashkey.
--- =========================================================================
 cte_customer_classification AS (
     SELECT
         scl.customer_hashkey,
@@ -368,35 +428,20 @@
     WHERE scl.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY scl.customer_hashkey
 ),
--- =========================================================================
--- 7. T_DESCRIPTION: ref_t24_sector theo ref_code = scl.sector
---    Dedup theo ref_code. LƯU Ý: bảng ref này không có source_event_date
---    trong nguồn gốc (dùng ORDER BY chính ref_code làm cột dedup arbitrary
---    trong bản cũ). Giữ nguyên hành vi arbitrary-pick-1-dòng/ref_code bằng
---    MAX(ref_description) — nếu ref_t24_sector thực có source_event_date,
---    cần đổi lại thành GROUP BY ref_code + MAX_BY(ref_description, source_event_date).
--- =========================================================================
 cte_sector_desc AS (
     SELECT
         rts.ref_code,
-        MAX(rts.ref_description) AS t_description
+        max_by(rts.ref_description, rts.source_event_date) AS t_description
     FROM IDENTIFIER(:cleaned || '.raw_vault.ref_t24_sector') rts
+    WHERE rts.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY rts.ref_code
 ),
--- =========================================================================
--- 9. CUST_GROUP_NAME: ref_t24_ocbh_cus_group.ref_description
---    theo ref_code = scl.cust_group. Dedup theo ref_code (cùng lưu ý như
---    cte_sector_desc ở trên).
--- 10,11. CUST_GROUP_LINE / CUST_GROUP_LINE_SHORT: bảng danh mục mnl_ocbh_cust_group
---    (gold layer, catalog :curated, schema tckh -- cùng cơ chế upload thủ công
---    như gl_param/mnl_card_pln_out), join theo custgroup_id = cst_grp và
---    data_date = ngày ETL.
--- =========================================================================
 cte_cust_group AS (
     SELECT
         ocg.ref_code,
-        MAX(ocg.ref_description) AS cust_group_name   -- cột 9
+        max_by(ocg.ref_description, ocg.source_event_date) AS cust_group_name   -- cột 9
     FROM IDENTIFIER(:cleaned || '.raw_vault.ref_t24_ocbh_cus_group') ocg
+    WHERE ocg.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY ocg.ref_code
 ),
 cte_mnl_cust_group AS (
@@ -407,12 +452,6 @@
     FROM IDENTIFIER(:curated || '.tckh.mnl_ocbh_cust_group')
     -- WHERE data_date = to_date(:DATADT, 'yyyyMMdd')
 ),
--- =========================================================================
--- 12,13. TIENGUI / TIENVAY: business_vault.csat_customer_sum_balance
---    Lọc: max(source_event_date) &lt;= [ETL]. Dedup theo customer_hashkey.
---    Lấy kèm so_du_bao_lanh/so_du_lc (cùng bảng) để tính BAOLANH_LC cho
---    T24_STATUS bên dưới (BAOLANH_LC = SO_DU_BAO_LANH + SO_DU_LC).
--- =========================================================================
 cte_customer_balance AS (
     SELECT
         ccb.customer_hashkey,
@@ -424,20 +463,6 @@
     WHERE ccb.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY ccb.customer_hashkey
 ),
--- =========================================================================
--- 14. CUST_CURRENT_ACCT_A1  (số dư TK thanh toán KKH - TGTT1KKH)
---    Theo mapping (4 bước, tầng Data Vault):
---    B1: account gắn CIF qua link_account_customer -&gt; hub_account
---        + sat_account_balance (t_currency), sat_account_classification
---          (t_condition_group), ref_t24_acct_group_condition (t_minimum_bal).
---    B2: chỉ giữ TK thanh toán (GL_TYPE 'TGTT1KKH'), loại GL tiết kiệm KKH/
---        tiền gửi/ký quỹ; số dư &gt;= mức tối thiểu.
---    B3: bổ sung TK số dư = 0 thỏa mức tối thiểu, chưa có ở B2.
---    B4: UNION B2 + B3, SUM theo customer_hashkey.
---    Dedup: SUM đã group theo customer_hashkey nên 1 dòng/CIF.
---    Loại account đã xóa qua cte_account_sts_del (LEFT JOIN ... IS NULL,
---    thay cho NOT EXISTS — kết quả tập account active giữ nguyên).
--- =========================================================================
 cte_acct_base AS (   -- Bước 1
     SELECT
         lac.customer_hashkey,
@@ -446,8 +471,8 @@
         max_by(sab.t_currency,        lac.source_event_date) AS t_currency,
         max_by(sac.t_condition_group, lac.source_event_date) AS t_condition_group,
         max_by(mini.t_minimum_bal,    lac.source_event_date) AS t_minimum_bal
-    FROM IDENTIFIER(:cleaned || '.raw_vault.link_account_customer') lac
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_account') ha
+    FROM cte_snap_link_account_customer lac
+    JOIN cte_snap_hub_account ha
       ON ha.account_hashkey = lac.account_hashkey
     LEFT JOIN cte_account_sts_del d_acc
       ON d_acc.account_hashkey = ha.account_hashkey
@@ -456,8 +481,7 @@
             account_hashkey,
             max_by(t_open_actual_bal, source_event_date) AS t_open_actual_bal,
             max_by(t_currency,        source_event_date) AS t_currency
-        FROM IDENTIFIER(:cleaned || '.raw_vault.sat_account_balance')
-        WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+        FROM cte_snap_sat_account_balance
         GROUP BY account_hashkey
     ) sab ON sab.account_hashkey = ha.account_hashkey
     LEFT JOIN (
@@ -471,20 +495,17 @@
     LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.ref_t24_acct_group_condition') mini
       ON mini.id = CONCAT(sac.t_condition_group, sab.t_currency)
     WHERE d_acc.account_hashkey IS NULL
-    -- lọc link_account_customer: giữ nguyên như bản gốc (không có
-    -- WHERE lac.source_event_date &lt;= [ETL] tường minh trong code cũ dù comment
-    -- có ghi; KHÔNG bổ sung ở đây theo đúng yêu cầu giữ nguyên logic)
     GROUP BY lac.customer_hashkey, lac.account_hashkey
 ),
-cte_acct_b2 AS (    -- Bước 2: TK thanh toán, số dư &gt;= mức tối thiểu
+cte_acct_b2 AS (    
     SELECT
         lca.account_hashkey,
         max_by(b.customer_hashkey,  lca.source_event_date) AS customer_hashkey,
         max_by(b.t_open_actual_bal, lca.source_event_date) AS t_open_actual_bal
     FROM cte_acct_base b
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.link_crb_account') lca
+    JOIN cte_link_crb_account_cur lca
       ON lca.account_hashkey = b.account_hashkey
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_crb') hcrb
+    JOIN cte_snap_hub_crb hcrb
       ON hcrb.crb_hashkey = lca.crb_hashkey
     LEFT JOIN cte_crb_sts_del d_crb
       ON d_crb.crb_hashkey = hcrb.crb_hashkey
@@ -507,7 +528,7 @@
       AND NVL(b.t_open_actual_bal, 0) = 0
       AND b.account_hashkey NOT IN (SELECT account_hashkey FROM cte_acct_b2)
 ),
-cte_cust_current_acct_a1 AS (   -- Bước 4: UNION + SUM theo CIF
+cte_cust_current_acct_a1 AS (   
     SELECT
         customer_hashkey,
         CAST(SUM(NVL(ABS(t_open_actual_bal), 0)) AS DECIMAL(20,4)) AS cust_current_acct_a1
@@ -518,19 +539,13 @@
     )
     GROUP BY customer_hashkey
 ),
--- =========================================================================
--- TOL_BAL_CUST_A3 (không xuất cột, chỉ dùng cho T24_STATUS/IsActive):
---    SUM số dư TK thuộc nhóm GL tiết kiệm KKH/tiền gửi/ký quỹ (14 mã GL) --
---    cùng danh sách GL bị loại trừ khỏi CUST_CURRENT_ACCT_A1 ở trên.
---    Loại account/crb đã xóa qua cte_account_sts_del / cte_crb_sts_del.
--- =========================================================================
 cte_tol_bal_a3_base AS (
     SELECT
         lac.customer_hashkey,
         lac.account_hashkey,
         max_by(sab.t_open_actual_bal, lac.source_event_date) AS t_open_actual_bal
-    FROM IDENTIFIER(:cleaned || '.raw_vault.link_account_customer') lac
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_account') ha
+    FROM cte_snap_link_account_customer lac
+    JOIN cte_snap_hub_account ha
       ON ha.account_hashkey = lac.account_hashkey
     LEFT JOIN cte_account_sts_del d_acc
       ON d_acc.account_hashkey = ha.account_hashkey
@@ -538,13 +553,12 @@
         SELECT
             account_hashkey,
             max_by(t_open_actual_bal, source_event_date) AS t_open_actual_bal
-        FROM IDENTIFIER(:cleaned || '.raw_vault.sat_account_balance')
-        WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+        FROM cte_snap_sat_account_balance
         GROUP BY account_hashkey
     ) sab ON sab.account_hashkey = ha.account_hashkey
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.link_crb_account') lca
+    JOIN cte_link_crb_account_cur lca
       ON lca.account_hashkey = ha.account_hashkey
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_crb') hcrb
+    JOIN cte_snap_hub_crb hcrb
       ON hcrb.crb_hashkey = lca.crb_hashkey
     LEFT JOIN cte_crb_sts_del d_crb
       ON d_crb.crb_hashkey = hcrb.crb_hashkey
@@ -560,12 +574,7 @@
     FROM cte_tol_bal_a3_base
     GROUP BY customer_hashkey
 ),
--- =========================================================================
--- 16. DOANHSO_BAOLANH_30D: SUM số dư hợp đồng bảo lãnh theo KH (value_date 30D)
---    Theo mapping (3 bước). Dedup ở output cuối bằng GROUP BY customer_hashkey.
---    Loại md_deal đã xóa qua cte_md_deal_sts_del.
--- =========================================================================
-cte_md_30d AS (     -- Bước 1: HĐ có value_date trong 30 ngày
+cte_md_30d AS (     
     SELECT
         smdi.md_deal_hashkey,
         max_by(smdi.t_value_date, smdi.source_event_date) AS value_date
@@ -577,36 +586,32 @@
       AND d_md.md_deal_hashkey IS NULL
     GROUP BY smdi.md_deal_hashkey
 ),
-cte_md_b2 AS (      -- Bước 2: value_date = ngày làm việc (calendar), lấy số dư crb
+cte_md_b2 AS (      
     SELECT
         md1.md_deal_hashkey,
         scb.noite
     FROM cte_md_30d md1
-    JOIN IDENTIFIER(:cleaned || '.business_vault.calendar') cal
+    JOIN cte_snap_calendar cal
       ON md1.value_date = cal.msr_prd_id AND cal.bsn_day_f = 1
     JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_md_deal') hmd
       ON hmd.md_deal_hashkey = md1.md_deal_hashkey
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_crb') hcb
+    JOIN cte_snap_hub_crb hcb
       ON hcb.tieukhoan = hmd.business_key AND hcb.gl &lt;&gt; '9995'
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_crb_balance') scb
+    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_crb_balance') scb
       ON scb.crb_hashkey = hcb.crb_hashkey
      AND scb.ma_key BETWEEN date_format(DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30), 'yyyyMMdd') AND :DATADT
+     AND scb.source_event_date = to_date(:DATADT, 'yyyyMMdd')
 ),
-cte_doanhso_baolanh_30d AS (    -- Bước 3: SUM theo customer_hashkey
+cte_doanhso_baolanh_30d AS (  
     SELECT
         lcif.customer_hashkey,
-        CAST(SUM(b2.noite) AS DECIMAL(31,4)) AS doanhso_baolanh_30d
+        CAST(SUM(NVL(b2.noite, 0)) AS DECIMAL(31,4)) AS doanhso_baolanh_30d
     FROM cte_md_b2 b2
-    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.link_md_deal_customer') lcif
+    LEFT JOIN cte_link_md_deal_customer_cur lcif
       ON lcif.md_deal_hashkey = b2.md_deal_hashkey
-     AND lcif.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY lcif.customer_hashkey
 ),
--- =========================================================================
--- 17. DOANHSO_LC_30D: SUM giá trị HĐ LC (applicant + beneficiary) theo CIF
---    Theo mapping (3 bước). Dedup ở output cuối bằng GROUP BY customer_hashkey.
--- =========================================================================
-cte_lc_30d AS (     -- Bước 1: LC phát hành mới trong 30 ngày
+cte_lc_30d AS (    
     SELECT
         slct.letter_of_credit_hashkey,
         max_by(slct.t_issue_date, slct.source_event_date) AS t_issue_date
@@ -615,38 +620,42 @@
       AND slct.t_issue_date BETWEEN date_format(DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30), 'yyyyMMdd') AND :DATADT
     GROUP BY slct.letter_of_credit_hashkey
 ),
-cte_lc_value AS (   -- giá trị LC (min amount, currency)
+cte_lc_value AS (  
     SELECT
         lc.letter_of_credit_hashkey,
         MIN(lc.t_issue_date)     AS issue_date,
         MIN(slcv.t_lc_amount)    AS first_lc_amount,
         slcv.t_lc_currency
     FROM cte_lc_30d lc
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_letter_of_credit_value') slcv
+    LEFT JOIN (
+        SELECT
+            letter_of_credit_hashkey,
+            max_by(t_lc_amount,   source_event_date) AS t_lc_amount,
+            max_by(t_lc_currency, source_event_date) AS t_lc_currency
+        FROM IDENTIFIER(:cleaned || '.raw_vault.sat_letter_of_credit_value')
+        WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+        GROUP BY letter_of_credit_hashkey
+    ) slcv
       ON slcv.letter_of_credit_hashkey = lc.letter_of_credit_hashkey
     GROUP BY lc.letter_of_credit_hashkey, slcv.t_lc_currency
 ),
-cte_lc_customer AS ( -- Bước 2: applicant UNION ALL beneficiary
-    -- 2.1 Applicant
+cte_lc_customer AS ( 
     SELECT
         llcc.customer_hashkey,
         llcc.letter_of_credit_hashkey
-    FROM IDENTIFIER(:cleaned || '.raw_vault.link_letter_of_credit_customer') llcc
+    FROM cte_snap_link_letter_of_credit_customer llcc
     WHERE llcc.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     UNION ALL
-    -- 2.2 Beneficiary (giữ nguyên join thẳng hub_customer như bản gốc,
-    -- không qua base_customer/cte_customer_active theo đúng yêu cầu không
-    -- đổi logic — đã lưu ý riêng ở các lượt trước, KHÔNG sửa ở đây)
     SELECT
         hc.customer_hashkey,
         prt.letter_of_credit_hashkey
     FROM IDENTIFIER(:cleaned || '.raw_vault.sat_letter_of_credit_party') prt
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_customer') hc
+    JOIN cte_snap_hub_customer hc
       ON hc.business_key = prt.t_beneficiary_custno
     WHERE prt.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
       AND prt.t_beneficiary_custno IS NOT NULL
 ),
-cte_doanhso_lc_30d AS (     -- Bước 3: quy đổi tỷ giá, SUM theo CIF
+cte_doanhso_lc_30d AS (   
     SELECT
         cust.customer_hashkey,
         CAST(SUM(
@@ -654,7 +663,7 @@
             NVL(CAST(REGEXP_EXTRACT(rc.t_mid_reval_rate, '[^:]+', 0) AS DECIMAL(20,8)), 0)
         ) AS DECIMAL(31,4)) AS doanhso_lc_30d
     FROM cte_lc_value v
-    JOIN IDENTIFIER(:cleaned || '.business_vault.calendar') cal
+    JOIN cte_snap_calendar cal
       ON v.issue_date = cal.msr_prd_id AND cal.bsn_day_f = 1
     JOIN IDENTIFIER(:cleaned || '.raw_vault.ref_currency') rc
       ON rc.id = v.t_lc_currency
@@ -664,29 +673,11 @@
       ON cust.letter_of_credit_hashkey = v.letter_of_credit_hashkey
     GROUP BY cust.customer_hashkey
 ),
--- =========================================================================
--- 18. NUM_TRANS: đếm số bút toán 30D/90D từ hub_stmt_entry + hub_categ_entry.
---    (Giữ nguyên: cte_link_account_customer_cur ở đây KHÔNG loại account đã
---    xóa, đúng như bản gốc — không bổ sung anti-join theo yêu cầu không đổi
---    logic.)
---    Loại: business_key like 'F%', transaction_code = 381, inputter chứa
---    '_COB' (đúng nguyên văn mapping: 1 dấu gạch dưới trước COB, không có
---    gạch dưới sau), bút toán trùng funds_transfer/teller đã bị đảo (REVE) hoặc
---    thuộc nhóm phí ACFx. Ghi CÓ (t_amount_lcy &lt; 0): đếm từng bút toán.
---    Ghi NỢ: KHÔNG đếm từng bút toán, mà GỘP (union) tổng ghi nợ cả 2 nguồn
---    stmt + categ theo CIF trong kỳ, nếu &gt; 100,000 thì cộng thêm đúng 1 giao
---    dịch (ngưỡng áp 1 lần trên tập gộp, đúng DataStage cũ trên PST_ENTR).
---    GIẢ ĐỊNH cần business xác nhận lại bằng dữ liệu mẫu:
---    (1) cách tách business_key dạng "PREFIX;N" lấy bản ghi N lớn nhất;
---    (2) cách cắt T_TRANS_REFERENCE trước dấu "\";
---    (3) pattern loại trừ input '_COB' (underscore là ký tự đại diện
---        trong LIKE nên đã escape thành literal).
--- =========================================================================
 cte_link_account_customer_cur AS (
     SELECT
         account_hashkey,
         max_by(customer_hashkey, source_event_date) AS customer_hashkey
-    FROM IDENTIFIER(:cleaned || '.raw_vault.link_account_customer')
+    FROM cte_snap_link_account_customer
     WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY account_hashkey
 ),
@@ -702,90 +693,94 @@
     SELECT
         letter_of_credit_hashkey,
         max_by(customer_hashkey, source_event_date) AS customer_hashkey
-    FROM IDENTIFIER(:cleaned || '.raw_vault.link_letter_of_credit_customer')
+    FROM cte_snap_link_letter_of_credit_customer
     WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY letter_of_credit_hashkey
 ),
-cte_ft_dedup AS (   -- funds_transfer: 1 dòng/prefix, giữ số thứ tự (";N") lớn nhất
+cte_ft_dedup AS (  
     SELECT
         max_by(hft.business_key,      TRY_CAST(split_part(hft.business_key, ';', 2) AS INT)) AS gd_id,
         max_by(fti.t_record_status,    TRY_CAST(split_part(hft.business_key, ';', 2) AS INT)) AS t_record_status,
         max_by(fti.t_transaction_type, TRY_CAST(split_part(hft.business_key, ';', 2) AS INT)) AS t_transaction_type
     FROM IDENTIFIER(:cleaned || '.raw_vault.hub_funds_transfer') hft
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_funds_transfer_information') fti
+    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_funds_transfer_information') fti
       ON fti.funds_transfer_hashkey = hft.funds_transfer_hashkey
+     AND fti.source_event_date = to_date(:DATADT, 'yyyyMMdd')
     GROUP BY split_part(hft.business_key, ';', 1)
 ),
-cte_tt_dedup AS (   -- teller: cùng quy tắc dedup theo prefix
+cte_tt_dedup AS (
     SELECT
         max_by(tt.business_key,     TRY_CAST(split_part(tt.business_key, ';', 2) AS INT)) AS gd_id,
         max_by(tti.t_record_status, TRY_CAST(split_part(tt.business_key, ';', 2) AS INT)) AS t_record_status
     FROM IDENTIFIER(:cleaned || '.raw_vault.hub_teller') tt
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_teller_information') tti
+    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_teller_information') tti
       ON tti.teller_hashkey = tt.teller_hashkey
+     AND tti.source_event_date = to_date(:DATADT, 'yyyyMMdd')
     GROUP BY split_part(tt.business_key, ';', 1)
 ),
-cte_reve_gd AS (    -- bút toán bị đảo (REVE) qua FT hoặc teller
+cte_reve_gd AS (  
     SELECT gd_id FROM cte_ft_dedup WHERE t_record_status = 'REVE'
     UNION
     SELECT gd_id FROM cte_tt_dedup WHERE t_record_status = 'REVE'
 ),
-cte_acfx_gd AS (    -- bút toán phí FT nhóm ACFx
+cte_acfx_gd AS (   
     SELECT gd_id FROM cte_ft_dedup
     WHERE t_transaction_type IN ('ACF3','ACF9','ACFN','ACF5','ACF6','ACF8','ACF7','ACF0','ACF2','ACF4','ACFS')
 ),
-cte_stmt_txn_base AS (    -- Bước 1: bút toán từ stmt_entry, gắn CIF qua tài khoản
+cte_stmt_txn_base AS (   
     SELECT
         lac.customer_hashkey,
         hst.source_event_date,
         info.t_amount_lcy
     FROM IDENTIFIER(:cleaned || '.raw_vault.hub_stmt_entry') hst
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_stmt_entry_information') info
+    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_stmt_entry_information') info
       ON info.stmt_entry_hashkey = hst.stmt_entry_hashkey
      AND info.source_event_date = hst.source_event_date
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_stmt_entry_classification') cls1
+    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_stmt_entry_classification') cls1
       ON cls1.stmt_entry_hashkey = hst.stmt_entry_hashkey
      AND cls1.source_event_date = hst.source_event_date
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_stmt_entry_audit') ad1
+    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_stmt_entry_audit') ad1
       ON ad1.stmt_entry_hashkey = hst.stmt_entry_hashkey
      AND ad1.source_event_date = hst.source_event_date
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_account') ha
+    JOIN cte_snap_hub_account ha
       ON ha.business_key = info.t_account_number
     JOIN cte_link_account_customer_cur lac
       ON lac.account_hashkey = ha.account_hashkey
+    LEFT JOIN cte_reve_gd r ON r.gd_id = split_part(info.t_trans_reference, '\\', 1)
+    LEFT JOIN cte_acfx_gd a ON a.gd_id = split_part(info.t_trans_reference, '\\', 1)
     WHERE hst.source_event_date BETWEEN DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -90) AND to_date(:DATADT, 'yyyyMMdd')
       AND hst.business_key NOT LIKE 'F%'
       AND cls1.t_transaction_code &lt;&gt; 381
       AND (ad1.t_inputter IS NULL OR ad1.t_inputter NOT LIKE '%\\_COB%' ESCAPE '\\')
-      AND NOT EXISTS (SELECT 1 FROM cte_reve_gd r WHERE r.gd_id = split_part(info.t_trans_reference, '\\', 1))
-      AND NOT EXISTS (SELECT 1 FROM cte_acfx_gd a WHERE a.gd_id = split_part(info.t_trans_reference, '\\', 1))
+      AND r.gd_id IS NULL
+      AND a.gd_id IS NULL
 ),
 cte_stmt_txn_agg AS (
     SELECT
         customer_hashkey,
-        COUNT(CASE WHEN source_event_date &gt;= DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30) AND t_amount_lcy &lt; 0 THEN 1 END) AS credit_cnt_30d,
-        COUNT(CASE WHEN t_amount_lcy &lt; 0 THEN 1 END) AS credit_cnt_90d,
-        SUM(CASE WHEN source_event_date &gt;= DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30) AND t_amount_lcy &gt;= 0 THEN t_amount_lcy ELSE 0 END) AS debit_sum_30d,
+        COUNT(CASE WHEN DATEDIFF(to_date(:DATADT, 'yyyyMMdd'), source_event_date) &lt;= 30 AND t_amount_lcy &lt; 0 THEN 1 ELSE NULL END) AS credit_cnt_30d,
+        COUNT(CASE WHEN t_amount_lcy &lt; 0 THEN 1 ELSE NULL END) AS credit_cnt_90d,
+        SUM(CASE WHEN DATEDIFF(to_date(:DATADT, 'yyyyMMdd'), source_event_date) &lt;= 30 AND t_amount_lcy &gt;= 0 THEN t_amount_lcy ELSE 0 END) AS debit_sum_30d,
         SUM(CASE WHEN t_amount_lcy &gt;= 0 THEN t_amount_lcy ELSE 0 END) AS debit_sum_90d
     FROM cte_stmt_txn_base
     GROUP BY customer_hashkey
 ),
-cte_categ_txn_base AS (    -- Bước 2: bút toán từ categ_entry, gắn CIF qua account/loan/LC theo t_system_id
+cte_categ_txn_base AS ( 
     SELECT
         NVL(lac.customer_hashkey, NVL(llnc.customer_hashkey, llcc.customer_hashkey)) AS customer_hashkey,
         ce.source_event_date,
         info.t_amount_lcy
     FROM IDENTIFIER(:cleaned || '.raw_vault.hub_categ_entry') ce
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_categ_entry_information') info
+    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_categ_entry_information') info
       ON info.categ_entry_hashkey = ce.categ_entry_hashkey
      AND info.source_event_date = ce.source_event_date
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_categ_entry_classification') cls1
+    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_categ_entry_classification') cls1
       ON cls1.categ_entry_hashkey = ce.categ_entry_hashkey
      AND cls1.source_event_date = ce.source_event_date
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_categ_entry_audit') ad1
+    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_categ_entry_audit') ad1
       ON ad1.categ_entry_hashkey = ce.categ_entry_hashkey
      AND ad1.source_event_date = ce.source_event_date
-    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_account') ha
+    LEFT JOIN cte_snap_hub_account ha
       ON ha.business_key = CASE
             WHEN cls1.t_system_id = 'AC' AND LEFT(info.t_our_reference, 2) = 'AZ'
                 THEN SUBSTR(info.t_our_reference, 4, 16)
@@ -808,28 +803,27 @@
          END
     LEFT JOIN cte_link_lc_customer_cur llcc
       ON llcc.letter_of_credit_hashkey = hlc.letter_of_credit_hashkey
+    LEFT JOIN cte_reve_gd r ON r.gd_id = split_part(info.t_trans_reference, '\\', 1)
+    LEFT JOIN cte_acfx_gd a ON a.gd_id = split_part(info.t_trans_reference, '\\', 1)
     WHERE ce.source_event_date BETWEEN DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -90) AND to_date(:DATADT, 'yyyyMMdd')
       AND ce.business_key NOT LIKE 'F%'
       AND cls1.t_transaction_code &lt;&gt; 381
       AND (ad1.t_inputter IS NULL OR ad1.t_inputter NOT LIKE '%\\_COB%' ESCAPE '\\')
-      AND NOT EXISTS (SELECT 1 FROM cte_reve_gd r WHERE r.gd_id = split_part(info.t_trans_reference, '\\', 1))
-      AND NOT EXISTS (SELECT 1 FROM cte_acfx_gd a WHERE a.gd_id = split_part(info.t_trans_reference, '\\', 1))
+      AND r.gd_id IS NULL
+      AND a.gd_id IS NULL
       AND NVL(lac.customer_hashkey, NVL(llnc.customer_hashkey, llcc.customer_hashkey)) IS NOT NULL
 ),
 cte_categ_txn_agg AS (
     SELECT
         customer_hashkey,
-        COUNT(CASE WHEN source_event_date &gt;= DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30) AND t_amount_lcy &lt; 0 THEN 1 END) AS credit_cnt_30d,
-        COUNT(CASE WHEN t_amount_lcy &lt; 0 THEN 1 END) AS credit_cnt_90d,
-        SUM(CASE WHEN source_event_date &gt;= DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30) AND t_amount_lcy &gt;= 0 THEN t_amount_lcy ELSE 0 END) AS debit_sum_30d,
+        COUNT(CASE WHEN DATEDIFF(to_date(:DATADT, 'yyyyMMdd'), source_event_date) &lt;= 30 AND t_amount_lcy &lt; 0 THEN 1 ELSE NULL END) AS credit_cnt_30d,
+        COUNT(CASE WHEN t_amount_lcy &lt; 0 THEN 1 ELSE NULL END) AS credit_cnt_90d,
+        SUM(CASE WHEN DATEDIFF(to_date(:DATADT, 'yyyyMMdd'), source_event_date) &lt;= 30 AND t_amount_lcy &gt;= 0 THEN t_amount_lcy ELSE 0 END) AS debit_sum_30d,
         SUM(CASE WHEN t_amount_lcy &gt;= 0 THEN t_amount_lcy ELSE 0 END) AS debit_sum_90d
     FROM cte_categ_txn_base
     GROUP BY customer_hashkey
 ),
-cte_num_trans AS (    -- Bước 3: GỘP (union) stmt + categ theo KH. Ghi CÓ (amount&lt;0):
-                      -- đếm từng bút toán, cộng count 2 nguồn. Ghi NỢ: GỘP tổng nợ
-                      -- cả 2 nguồn (= tổng trên tập union) rồi so ngưỡng &gt;100,000 CHỈ
-                      -- 1 lần -&gt; tối đa +1 (đúng DataStage cũ chạy trên PST_ENTR gộp).
+cte_num_trans AS (  
     SELECT
         COALESCE(s.customer_hashkey, c.customer_hashkey) AS customer_hashkey,
         NVL(s.credit_cnt_30d, 0) + NVL(c.credit_cnt_30d, 0)
@@ -840,33 +834,13 @@
     FULL OUTER JOIN cte_categ_txn_agg c
       ON c.customer_hashkey = s.customer_hashkey
 ),
--- =========================================================================
--- 20. T24_STATUS: tự tham chiếu chính bảng đích (CST_LCS_KT_30D_FINAL_CASE5)
---    của các ngày ETL trước đó để lấy NEW_CUST/NON_DORMANT.
---    QUAN TRỌNG - ràng buộc vận hành: job PHẢI chạy tuần tự theo đúng thứ tự
---    ngày (không backfill song song/ngoài thứ tự), vì kết quả ngày N phụ
---    thuộc FINAL_STATUS đã commit của (tối đa) 181 ngày trước đó.
---    (Giữ nguyên như bản gốc, kể cả việc cte_non_dormant bao gồm cả DATADT
---    đang chạy trong cận trên — đã lưu ý riêng ở lượt trước, KHÔNG sửa ở đây.)
---    Bước 1: NEW_CUST = 1 nếu ngày làm việc liền trước KHÔNG có bản ghi
---    final_status = 'ORIGINAL' cho CIF này; NON_DORMANT = số ngày trong 181
---    ngày gần nhất mà final_status KHÔNG thuộc ('DORMANT','LOST').
---    SRC_LCS_TP_ID = NEW_CUST=1 -&gt; 'ORIGINAL'; else NON_DORMANT&gt;0 -&gt; 'DORMANT'
---    (từng active gần đây nhưng không phải hôm nay); else 'LOST'.
---    Bước 2: IsActive theo nhánh CST_GRP[1,1], dùng TIENGUI, TOL_BAL_CUST_A3,
---    CUST_CURRENT_ACCT_A1 + NUM_TRANS, TIENVAY + CIF_LOANCLASS, và BAOLANH_LC
---    (= so_du_bao_lanh + so_du_lc, business_vault.csat_customer_sum_balance).
---    Bước 3: IsActive=1 -&gt; 'ACTIVE'; else SRC_LCS_TP_ID (nhánh
---    IsActive=0 AND SRC_LCS_TP_ID='ACTIVE' -&gt; 'DORMANT' không bao giờ khớp vì
---    SRC_LCS_TP_ID chỉ nhận ORIGINAL/DORMANT/LOST -- giữ lại để đúng mapping).
--- =========================================================================
-cte_prev_bsn_day AS (   -- ngày làm việc liền trước ETL_DATE
+cte_prev_bsn_day AS (   
     SELECT MAX(msr_prd_id) AS prev_bsn_day
-    FROM IDENTIFIER(:cleaned || '.business_vault.calendar')
+    FROM cte_snap_calendar
     WHERE bsn_day_f = 1
       AND msr_prd_id &lt; to_date(:DATADT, 'yyyyMMdd')
 ),
-cte_new_cust AS (   -- NEW_CUST: ngày làm việc trước KHÔNG có final_status = 'ORIGINAL'
+cte_new_cust AS (  
     SELECT bc.customer_hashkey
     FROM base_customer bc
     CROSS JOIN cte_prev_bsn_day pd
@@ -878,7 +852,7 @@
           AND prev.data_dt = pd.prev_bsn_day
     )
 ),
-cte_non_dormant AS (   -- NON_DORMANT: số ngày trong 181D gần nhất không DORMANT/LOST
+cte_non_dormant AS (  
     SELECT
         prev.cif,
         SUM(CASE WHEN prev.final_status NOT IN ('DORMANT', 'LOST') THEN 1 ELSE 0 END) AS non_dormant
@@ -895,7 +869,396 @@
             ELSE 'LOST'
         END AS src_lcs_tp_id
     FROM base_customer bc
-    LEF</t>
+    LEFT JOIN cte_new_cust nc ON nc.customer_hashkey = bc.customer_hashkey
+    LEFT JOIN cte_non_dormant nd ON nd.cif = bc.cif
+),
+cte_t24_status AS (
+    SELECT
+        bc.customer_hashkey,
+        CASE WHEN LEFT(cc.cst_grp, 1) IN ('1', '5') THEN
+            CASE
+                WHEN NVL(bal.tiengui, 0) &gt; 0 THEN 1
+                WHEN NVL(a3.tol_bal_cust_a3, 0) &gt; 0 THEN 1
+                WHEN NVL(a1.cust_current_acct_a1, 0) &gt;= 0 AND NVL(nt.num_trans_30d, 0) &gt; 0 THEN 1
+                WHEN NVL(bal.tienvay, 0) &gt; 0 AND NVL(cc.cif_loanclass, 1) &lt;= 2 THEN 1
+                WHEN NVL(bal.tienvay, 0) &gt; 0 AND NVL(cc.cif_loanclass, 1) &gt; 2 AND NVL(nt.num_trans_30d, 0) &gt; 0 THEN 1
+                WHEN NVL(bal.so_du_bao_lanh, 0) + NVL(bal.so_du_lc, 0) &gt; 0 THEN 1
+                ELSE 0
+            END
+        ELSE
+            CASE
+                WHEN NVL(bal.tiengui, 0) &gt; 0 THEN 1
+                WHEN NVL(a3.tol_bal_cust_a3, 0) &gt; 0 THEN 1
+                WHEN NVL(a1.cust_current_acct_a1, 0) &gt;= 0 AND NVL(nt.num_trans_90d, 0) &gt; 0 THEN 1
+                WHEN NVL(bal.tienvay, 0) &gt; 0 AND NVL(cc.cif_loanclass, 1) &lt;= 2 THEN 1
+                WHEN NVL(bal.tienvay, 0) &gt; 0 AND NVL(cc.cif_loanclass, 1) &gt; 2 AND NVL(nt.num_trans_90d, 0) &gt; 0 THEN 1
+                WHEN NVL(bal.so_du_bao_lanh, 0) + NVL(bal.so_du_lc, 0) &gt; 0 THEN 1
+                ELSE 0
+            END
+        END AS is_active,
+        st.src_lcs_tp_id
+    FROM base_customer bc
+    LEFT JOIN cte_customer_classification cc ON cc.customer_hashkey = bc.customer_hashkey
+    LEFT JOIN cte_customer_balance bal ON bal.customer_hashkey = bc.customer_hashkey
+    LEFT JOIN cte_tol_bal_a3 a3 ON a3.customer_hashkey = bc.customer_hashkey
+    LEFT JOIN cte_cust_current_acct_a1 a1 ON a1.customer_hashkey = bc.customer_hashkey
+    LEFT JOIN cte_num_trans nt ON nt.customer_hashkey = bc.customer_hashkey
+    LEFT JOIN cte_src_lcs_tp st ON st.customer_hashkey = bc.customer_hashkey
+),
+cte_t24_status_final AS (
+    SELECT
+        customer_hashkey,
+        CASE
+            WHEN is_active = 1 THEN 'ACTIVE'
+            WHEN is_active = 0 AND src_lcs_tp_id = 'ACTIVE' THEN 'DORMANT'
+            ELSE src_lcs_tp_id
+        END AS t24_status
+    FROM cte_t24_status
+),
+cte_ref_way4_contr_status_cur AS (
+    SELECT
+        id,
+        max_by(code, source_event_date) AS code
+    FROM IDENTIFIER(:cleaned || '.raw_vault.ref_way4_contr_status')
+    WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY id
+),
+cte_w4_acnt_contract_info_cur AS (   
+    SELECT
+        acnt_contract_hashkey,
+        max_by(contract_number, source_event_date) AS contract_number,
+        max_by(contr_status,    source_event_date) AS contr_status
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_acnt_contract_information')
+    WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY acnt_contract_hashkey
+),</t>
+  </si>
+  <si>
+    <t>cte_w4_acnt_contract_type_cur AS (   
+    SELECT
+        acnt_contract_hashkey,
+        max_by(con_cat,  source_event_date) AS con_cat,
+        max_by(ext_data, source_event_date) AS ext_data
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_acnt_contract_type')
+    WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY acnt_contract_hashkey
+),
+cte_w4_acnt_contract_branch_cur AS (
+    SELECT
+        acnt_contract_hashkey,
+        max_by(branch_hashkey, source_event_date) AS branch_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.link_acnt_contract_branch')
+    WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY acnt_contract_hashkey
+),
+cte_w4_acnt_contract_product_cur AS (
+    SELECT
+        acnt_contract_hashkey,
+        max_by(product_hashkey, source_event_date) AS product_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.link_acnt_contract_product')
+    WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY acnt_contract_hashkey
+),
+cte_w4_acnt_contract_client_cur AS (
+    SELECT
+        acnt_contract_hashkey,
+        max_by(client_hashkey, source_event_date) AS client_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.link_acnt_contract_client')
+    WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY acnt_contract_hashkey
+),
+cte_w4_link_acc_contract_card_active AS (
+    SELECT
+        lacc.card_hashkey,
+        lacc.account_contract_hashkey,
+        lacc.source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.link_account_contract_card') lacc
+    WHERE lacc.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+),
+cte_w4_account_contract_card_cur AS (
+    SELECT
+        lacc.card_hashkey,
+        max_by(lacc.account_contract_hashkey, lacc.source_event_date) AS account_contract_hashkey
+    FROM cte_w4_link_acc_contract_card_active lacc
+    JOIN cte_w4_acnt_contract_type_cur cc
+      ON cc.acnt_contract_hashkey = lacc.card_hashkey
+     AND cc.con_cat = 'C'
+    GROUP BY lacc.card_hashkey
+),
+cte_w4_product_info_cur AS (
+    SELECT
+        product_hashkey,
+        max_by(code, source_event_date) AS code
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_product_information')
+    WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY product_hashkey
+),
+cte_w4_balance_link_cur AS (
+    SELECT
+        balance_hashkey,
+        max_by(acnt_contract_hashkey, source_event_date) AS acnt_contract_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.link_balance_acnt_contract')
+    WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY balance_hashkey
+),
+cte_w4_balance_info_cur AS (
+    SELECT
+        balance_hashkey,
+        max_by(savings_balance,        source_event_date) AS savings_balance,
+        max_by(fixed_term_balance,     source_event_date) AS fixed_term_balance,
+        max_by(flexible_term_balance,  source_event_date) AS flexible_term_balance,
+        max_by(total_balance,          source_event_date) AS total_balance
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_balance_information')
+    WHERE source_event_date = to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY balance_hashkey
+),
+cte_w4_balance_principal_cur AS (
+    SELECT
+        balance_hashkey,
+        max_by(principal_balance, source_event_date) AS principal_balance
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_balance_principal')
+    WHERE source_event_date = to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY balance_hashkey
+),
+cte_w4_balance_instalment_cur AS (
+    SELECT
+        balance_hashkey,
+        max_by(instalment_balance, source_event_date) AS instalment_balance
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_balance_instalment')
+    WHERE source_event_date = to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY balance_hashkey
+),
+cte_w4_client_customer_cur AS (
+    SELECT
+        client_hashkey,
+        max_by(customer_hashkey, source_event_date) AS customer_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.link_client_customer')
+    WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY client_hashkey
+),
+cte_w4_loan_class AS (   
+    SELECT so_hd, loan_class
+    FROM IDENTIFIER(:curated || '.tckh.mnl_card_pln_out')
+    WHERE ngay_du_lieu = to_date(:DATADT, 'yyyyMMdd')
+),
+cte_w4_card_contract AS (
+    SELECT
+        lac.acnt_contract_hashkey                          AS issuing_hashkey,
+        max_by(cc.acnt_contract_hashkey, cc.business_key)  AS card_hashkey,
+        max_by(sci.contract_number,      cc.business_key)  AS issuing_number,
+        max_by(br.business_key,          cc.business_key)  AS branch_code,
+        max_by(
+            CASE WHEN LOCATE('LAST_TRANS_DATE', sty.ext_data) &gt; 0 THEN
+                SUBSTR(sty.ext_data,
+                    LOCATE('LAST_TRANS_DATE', sty.ext_data) + 16,
+                    LOCATE(';', sty.ext_data, LOCATE('LAST_TRANS_DATE', sty.ext_data) + 16)
+                        - LOCATE('LAST_TRANS_DATE', sty.ext_data) - 16)
+            ELSE NULL END,
+            cc.business_key
+        ) AS last_trans_date
+    FROM cte_w4_account_contract_card_cur lacc
+    JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_acnt_contract') cc
+      ON cc.acnt_contract_hashkey = lacc.card_hashkey
+    JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_acnt_contract') lac
+      ON lac.acnt_contract_hashkey = lacc.account_contract_hashkey
+    JOIN cte_w4_acnt_contract_info_cur scc
+      ON scc.acnt_contract_hashkey = cc.acnt_contract_hashkey    -- thông tin thẻ
+    JOIN cte_w4_acnt_contract_info_cur sci
+      ON sci.acnt_contract_hashkey = lac.acnt_contract_hashkey   -- thông tin issuing (contract_number)
+    JOIN cte_w4_acnt_contract_type_cur sty
+      ON sty.acnt_contract_hashkey = cc.acnt_contract_hashkey
+     AND sty.con_cat = 'C'                                         -- card
+    JOIN cte_w4_acnt_contract_type_cur ity
+      ON ity.acnt_contract_hashkey = lac.acnt_contract_hashkey
+     AND ity.con_cat = 'A'                                         -- issuing
+    JOIN cte_w4_acnt_contract_branch_cur lbr
+      ON lbr.acnt_contract_hashkey = cc.acnt_contract_hashkey
+    JOIN cte_snap_hub_branch br
+      ON br.branch_hashkey = lbr.branch_hashkey
+    JOIN cte_w4_acnt_contract_product_cur lpr
+      ON lpr.acnt_contract_hashkey = cc.acnt_contract_hashkey
+    JOIN cte_w4_product_info_cur sp
+      ON sp.product_hashkey = lpr.product_hashkey
+    JOIN cte_ref_way4_contr_status_cur rcs_c
+      ON rcs_c.id = scc.contr_status
+    JOIN cte_ref_way4_contr_status_cur rcs_i
+      ON rcs_i.id = sci.contr_status
+    WHERE SUBSTR(sp.code, 5, 1) = 'M'
+      AND rcs_i.code NOT IN ('13', '12', '33')    -- Account Closed / Waiting Closed
+      AND rcs_c.code NOT IN ('14', '65', '05', '09', '54', '37', '41', '29')  -- Card Closed/Lost/Expired/...
+    GROUP BY lac.acnt_contract_hashkey
+),
+cte_w4_balance AS (   
+    SELECT
+        lba.acnt_contract_hashkey AS issuing_hashkey,
+        sbi.savings_balance,
+        sbi.fixed_term_balance,
+        sbi.flexible_term_balance,
+        sbi.total_balance,
+        sbp.principal_balance,
+        sbn.instalment_balance
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_balance') hb
+    JOIN cte_w4_balance_link_cur lba ON lba.balance_hashkey = hb.balance_hashkey
+    JOIN cte_w4_balance_info_cur sbi ON sbi.balance_hashkey = hb.balance_hashkey
+    JOIN cte_w4_balance_principal_cur sbp ON sbp.balance_hashkey = hb.balance_hashkey
+    JOIN cte_w4_balance_instalment_cur sbn ON sbn.balance_hashkey = hb.balance_hashkey
+),
+cte_w4_issuing_status AS ( 
+    SELECT
+        ci.card_hashkey,
+        ci.issuing_hashkey,
+        ci.branch_code,
+        CASE
+            WHEN (ci.credit_amount = 1 AND ci.trans_30d = 1)
+              OR (ci.debit_amount = 1 AND NVL(ci.loan_class, 1) &lt;= 2)
+              OR (ci.debit_amount = 1 AND NVL(ci.loan_class, 1) &gt; 2 AND ci.trans_30d = 1)
+              OR (ci.debit_amount = 0 AND ci.trans_30d = 1)
+              OR (ci.credit_amount = 0 AND ci.trans_30d = 1) THEN 1   -- ACTIVE
+            WHEN ci.trans_31_120d = 1 THEN 2                        -- DORMANT
+            WHEN ci.trans_121d = 1 THEN 3                           -- LOST
+            ELSE 4                                                  -- ORIGINAL
+        END AS issuing_status_id
+    FROM (
+        SELECT
+            base.card_hashkey,
+            base.issuing_hashkey,
+            base.branch_code,
+            lcls.loan_class,
+            CASE WHEN NVL(bl.savings_balance, 0) &gt; 0 OR NVL(bl.fixed_term_balance, 0) &gt; 0
+                  OR NVL(bl.flexible_term_balance, 0) &gt; 0 OR NVL(bl.total_balance, 0) &gt; 0
+                 THEN 1 ELSE 0 END AS credit_amount,
+            CASE WHEN NVL(bl.principal_balance, 0) + NVL(bl.instalment_balance, 0) &lt; 0
+                 THEN 1 ELSE 0 END AS debit_amount,
+            CASE WHEN to_date(base.last_trans_date, 'yyyyMMdd')
+                       BETWEEN DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30) AND to_date(:DATADT, 'yyyyMMdd')
+                 THEN 1 ELSE 0 END AS trans_30d,
+            CASE WHEN to_date(base.last_trans_date, 'yyyyMMdd')
+                       BETWEEN DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -180) AND DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -31)
+                 THEN 1 ELSE 0 END AS trans_31_120d,
+            CASE WHEN to_date(base.last_trans_date, 'yyyyMMdd') &lt; DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -180)
+                  AND base.last_trans_date &gt; '19000101'
+                 THEN 1 ELSE 0 END AS trans_121d
+        FROM cte_w4_card_contract base
+        LEFT JOIN cte_w4_balance bl ON bl.issuing_hashkey = base.issuing_hashkey
+        LEFT JOIN cte_w4_loan_class lcls ON lcls.so_hd = base.issuing_number
+    ) ci
+),
+cte_w4_branch_customer AS (   
+    SELECT
+        bc.customer_hashkey,
+        s.branch_code,
+        s.issuing_status_id
+    FROM cte_w4_issuing_status s
+    JOIN cte_w4_acnt_contract_client_cur lcl
+      ON lcl.acnt_contract_hashkey = s.card_hashkey
+    JOIN cte_w4_client_customer_cur lcc
+      ON lcc.client_hashkey = lcl.client_hashkey
+    JOIN base_customer bc
+      ON bc.customer_hashkey = lcc.customer_hashkey
+     AND bc.cif &lt;&gt; 'INSTANTCARD'
+),
+cte_w4_branch_min AS (  
+    SELECT
+        customer_hashkey,
+        branch_code,
+        MIN(issuing_status_id) AS min_issuing_status_id
+    FROM cte_w4_branch_customer
+    GROUP BY customer_hashkey, branch_code
+),
+cte_w4_status AS (  
+    SELECT
+        customer_hashkey,
+        CASE MIN(min_issuing_status_id)
+            WHEN 1 THEN 'ACTIVE'
+            WHEN 2 THEN 'DORMANT'
+            WHEN 3 THEN 'LOST'
+            WHEN 4 THEN 'ORIGINAL'
+            ELSE NULL
+        END AS w4_status,
+        MAX(CASE WHEN branch_code &lt;&gt; 'VN0010182' AND min_issuing_status_id = 1 THEN 1 ELSE 0 END) AS w4_active_rb,
+        MAX(CASE WHEN branch_code = 'VN0010182' AND min_issuing_status_id = 1 THEN 1 ELSE 0 END) AS w4_active_lio
+    FROM cte_w4_branch_min
+    GROUP BY customer_hashkey
+)
+SELECT
+    to_date(:DATADT, 'yyyyMMdd')                          AS DATA_DT,                 -- 1
+    bc.cif                                      AS CIF,                    -- 2
+    cb.t_company_book                           AS T_COMPANY_BOOK,         -- 3
+    NVL(cd.t_create_date, bc.hc_first_load_date) AS T_CREATE_DATE,         -- 4
+    CASE GREATEST(
+            CASE t24s.t24_status WHEN 'ACTIVE' THEN 4 WHEN 'DORMANT' THEN 3 WHEN 'LOST' THEN 2 WHEN 'ORIGINAL' THEN 1 ELSE -1 END,
+            CASE w4.w4_status    WHEN 'ACTIVE' THEN 4 WHEN 'DORMANT' THEN 3 WHEN 'LOST' THEN 2 WHEN 'ORIGINAL' THEN 1 ELSE -1 END
+         )
+        WHEN 4 THEN 'ACTIVE'
+        WHEN 3 THEN 'DORMANT'
+        WHEN 2 THEN 'LOST'
+        WHEN 1 THEN 'ORIGINAL'
+        ELSE NULL
+    END                                          AS FINAL_STATUS,
+    cc.sctr                                     AS SCTR,                   -- 6
+    sd.t_description                            AS T_DESCRIPTION,          -- 7
+    cc.cst_grp                                  AS CST_GRP,                -- 8
+    cg.cust_group_name                          AS CUST_GROUP_NAME,        -- 9
+    mcg.cust_group_line                         AS CUST_GROUP_LINE,        -- 10
+    mcg.cust_group_line_short                   AS CUST_GROUP_LINE_SHORT,  -- 11
+    NVL(bal.tiengui, 0)                         AS TIENGUI,                -- 12
+    NVL(bal.tienvay, 0)                         AS TIENVAY,                -- 13
+    NVL(a1.cust_current_acct_a1, 0)             AS CUST_CURRENT_ACCT_A1,   -- 14
+    cc.cif_loanclass                            AS CIF_LOANCLASS,          -- 15
+    NVL(md.doanhso_baolanh_30d, 0)              AS DOANHSO_BAOLANH_30D,    -- 16
+    NVL(lc.doanhso_lc_30d, 0)                   AS DOANHSO_LC_30D,         -- 17
+    CASE WHEN LEFT(cc.cst_grp, 1) IN ('1', '5')
+         THEN NVL(nt.num_trans_30d, 0)
+         ELSE NVL(nt.num_trans_90d, 0)
+    END                                          AS NUM_TRANS,
+    CASE WHEN LEFT(cc.cst_grp, 1) IN ('1', '5') THEN
+        CASE
+            WHEN NVL(bal.tiengui, 0) &gt; 0 AND NVL(nt.num_trans_30d, 0) &gt; 0 THEN 1
+            WHEN NVL(a1.cust_current_acct_a1, 0) &gt; 0 AND NVL(nt.num_trans_30d, 0) &gt; 0 THEN 2
+            WHEN NVL(bal.tienvay, 0) &gt; 0 AND cc.cif_loanclass = 1 THEN 3
+            WHEN NVL(bal.tienvay, 0) &gt; 0 AND cc.cif_loanclass &gt; 1 AND NVL(nt.num_trans_30d, 0) &gt; 0 THEN 4
+            WHEN NVL(md.doanhso_baolanh_30d, 0) &gt; 0 THEN 5
+            WHEN NVL(lc.doanhso_lc_30d, 0) &gt; 0 THEN 6
+            ELSE 0
+        END
+    ELSE
+        CASE
+            WHEN NVL(bal.tiengui, 0) &gt; 0 AND NVL(nt.num_trans_90d, 0) &gt; 0 THEN 1
+            WHEN NVL(a1.cust_current_acct_a1, 0) &gt; 0 AND NVL(nt.num_trans_90d, 0) &gt; 0 THEN 2
+            WHEN NVL(bal.tienvay, 0) &gt; 0 AND cc.cif_loanclass = 1 THEN 3
+            WHEN NVL(bal.tienvay, 0) &gt; 0 AND cc.cif_loanclass &gt; 1 AND NVL(nt.num_trans_90d, 0) &gt; 0 THEN 4
+            WHEN NVL(md.doanhso_baolanh_30d, 0) &gt; 0 THEN 5
+            WHEN NVL(lc.doanhso_lc_30d, 0) &gt; 0 THEN 6
+            ELSE 0
+        END
+    END                                         AS ACTIVE_INDEX,
+    t24s.t24_status                             AS T24_STATUS,
+    CASE WHEN t24s.t24_status = 'ACTIVE' AND mcg.cust_group_line_short = 'KRB' THEN 1 ELSE 0 END       AS T24_ACTIVE_RB,   -- 21
+    CASE WHEN t24s.t24_status = 'ACTIVE' AND mcg.cust_group_line_short = 'COMB' THEN 1 ELSE 0 END      AS T24_ACTIVE_COMB, -- 22
+    CASE WHEN t24s.t24_status = 'ACTIVE' AND mcg.cust_group_line_short = 'TREASURY' THEN 1 ELSE 0 END  AS T24_ACTIVE_TRE,  -- 23
+    CASE WHEN t24s.t24_status = 'ACTIVE' AND mcg.cust_group_line_short = 'CIB' THEN 1 ELSE 0 END       AS T24_ACTIVE_CIB,  -- 24
+    CASE WHEN t24s.t24_status = 'ACTIVE' AND mcg.cust_group_line_short = 'SME' THEN 1 ELSE 0 END       AS T24_ACTIVE_CMB,  -- 25
+    CASE WHEN t24s.t24_status = 'ACTIVE' AND mcg.cust_group_line_short = 'KDCTC' THEN 1 ELSE 0 END     AS T24_ACTIVE_DCTC, -- 26
+    CASE WHEN t24s.t24_status = 'ACTIVE' AND mcg.cust_group_line_short = 'LIOBANK' THEN 1 ELSE 0 END   AS T24_ACTIVE_LIO,  -- 27
+    w4.w4_status                                AS W4_STATUS,              -- 28
+    NVL(w4.w4_active_rb, 0)                     AS W4_ACTIVE_RB,           -- 29
+    NVL(w4.w4_active_lio, 0)                    AS W4_ACTIVE_LIO,          -- 30
+    NULL                                        AS DATE_SYS                -- 31
+FROM base_customer bc
+LEFT JOIN cte_company_book             cb  ON cb.customer_hashkey  = bc.customer_hashkey
+LEFT JOIN cte_create_date              cd  ON cd.customer_hashkey  = bc.customer_hashkey
+LEFT JOIN cte_customer_classification  cc  ON cc.customer_hashkey  = bc.customer_hashkey
+LEFT JOIN cte_sector_desc              sd  ON sd.ref_code          = cc.sctr
+LEFT JOIN cte_cust_group               cg  ON cg.ref_code          = cc.cst_grp
+LEFT JOIN cte_mnl_cust_group           mcg ON mcg.custgroup_id      = cc.cst_grp
+LEFT JOIN cte_customer_balance         bal ON bal.customer_hashkey = bc.customer_hashkey
+LEFT JOIN cte_cust_current_acct_a1     a1  ON a1.customer_hashkey  = bc.customer_hashkey
+LEFT JOIN cte_doanhso_baolanh_30d      md  ON md.customer_hashkey  = bc.customer_hashkey
+LEFT JOIN cte_doanhso_lc_30d           lc  ON lc.customer_hashkey  = bc.customer_hashkey
+LEFT JOIN cte_num_trans                nt  ON nt.customer_hashkey  = bc.customer_hashkey
+LEFT JOIN cte_t24_status_final         t24s ON t24s.customer_hashkey = bc.customer_hashkey
+LEFT JOIN cte_w4_status                w4  ON w4.customer_hashkey  = bc.customer_hashkey
+;</t>
   </si>
   <si>
     <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
@@ -5232,7 +5595,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0BC621D-40BB-4371-8CAF-4175E066EA14}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="11"/>
@@ -5241,7 +5604,7 @@
     <col min="4" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1">
+    <row r="1" spans="1:6" ht="15.75" thickBot="1">
       <c r="A1" s="42" t="s">
         <v>24</v>
       </c>
@@ -5255,7 +5618,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="21" customHeight="1">
+    <row r="2" spans="1:6" ht="21" customHeight="1">
       <c r="A2" s="11" t="s">
         <v>28</v>
       </c>
@@ -5266,7 +5629,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:6">
       <c r="A3" s="11" t="s">
         <v>28</v>
       </c>
@@ -5280,7 +5643,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:6">
       <c r="A4" s="11" t="s">
         <v>28</v>
       </c>
@@ -5291,7 +5654,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:6">
       <c r="A5" s="11" t="s">
         <v>34</v>
       </c>
@@ -5302,7 +5665,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:6">
       <c r="A6" s="11" t="s">
         <v>34</v>
       </c>
@@ -5313,15 +5676,27 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:6">
       <c r="A7" s="11" t="s">
         <v>34</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>37</v>
+      </c>
+      <c r="F7"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -5345,7 +5720,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="42" customHeight="1">
       <c r="A1" s="93" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1" s="94"/>
       <c r="C1" s="94"/>
@@ -5354,19 +5729,19 @@
     </row>
     <row r="2" spans="1:6" ht="20.25" customHeight="1">
       <c r="A2" s="15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="27" customHeight="1">
@@ -5377,13 +5752,13 @@
         <v>10</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="101.25" customHeight="1">
@@ -5391,16 +5766,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -5419,7 +5794,7 @@
     </row>
     <row r="7" spans="1:6" ht="20.25" customHeight="1">
       <c r="A7" s="95" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7" s="96"/>
       <c r="C7" s="96"/>
@@ -5432,16 +5807,16 @@
         <v>25</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F8" s="18"/>
     </row>
@@ -5450,16 +5825,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -5467,16 +5842,16 @@
         <v>7</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -5484,16 +5859,16 @@
         <v>7</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -5501,16 +5876,16 @@
         <v>7</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -5518,16 +5893,16 @@
         <v>7</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -5535,16 +5910,16 @@
         <v>7</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -5572,7 +5947,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="51" customHeight="1">
       <c r="A1" s="106" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B1" s="69"/>
       <c r="C1" s="69"/>
@@ -5582,20 +5957,20 @@
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="43" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2" s="95" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" s="97"/>
       <c r="D2" s="44" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F2" s="43" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="222" customHeight="1">
@@ -5603,17 +5978,17 @@
         <v>1</v>
       </c>
       <c r="B3" s="107" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" s="108"/>
       <c r="D3" s="46" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E3" s="47" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F3" s="47" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="153.75" customHeight="1">
@@ -5621,14 +5996,14 @@
         <v>2</v>
       </c>
       <c r="B4" s="102" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C4" s="102"/>
       <c r="D4" s="52" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E4" s="53" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F4" s="53"/>
     </row>
@@ -5637,14 +6012,14 @@
         <v>3</v>
       </c>
       <c r="B5" s="109" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C5" s="110"/>
       <c r="D5" s="52" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E5" s="53" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F5" s="53"/>
     </row>
@@ -5653,17 +6028,17 @@
         <v>4</v>
       </c>
       <c r="B6" s="104" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6" s="104"/>
       <c r="D6" s="52" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E6" s="53" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F6" s="53" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="113.25" customHeight="1">
@@ -5671,14 +6046,14 @@
         <v>5</v>
       </c>
       <c r="B7" s="104" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C7" s="104"/>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E7" s="53" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F7" s="53"/>
     </row>
@@ -5687,14 +6062,14 @@
         <v>6</v>
       </c>
       <c r="B8" s="105" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C8" s="105"/>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E8" s="53" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F8" s="53"/>
     </row>
@@ -5703,14 +6078,14 @@
         <v>7</v>
       </c>
       <c r="B9" s="102" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C9" s="102"/>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E9" s="53" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F9" s="53"/>
     </row>
@@ -5719,15 +6094,15 @@
         <v>8</v>
       </c>
       <c r="B10" s="98" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" s="98"/>
       <c r="D10" s="54"/>
       <c r="E10" s="53" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F10" s="53" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="408.75" customHeight="1">
@@ -5735,15 +6110,15 @@
         <v>9</v>
       </c>
       <c r="B11" s="98" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C11" s="98"/>
       <c r="D11"/>
       <c r="E11" s="53" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="105" customHeight="1">
@@ -5751,15 +6126,15 @@
         <v>10</v>
       </c>
       <c r="B12" s="102" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C12" s="102"/>
       <c r="D12"/>
       <c r="E12" s="53" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F12" s="53" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="156.75" customHeight="1">
@@ -5767,15 +6142,15 @@
         <v>11</v>
       </c>
       <c r="B13" s="102" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C13" s="102"/>
       <c r="D13"/>
       <c r="E13" s="53" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F13" s="53" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="118.5" customHeight="1">
@@ -5783,17 +6158,17 @@
         <v>12</v>
       </c>
       <c r="B14" s="98" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C14" s="98"/>
       <c r="D14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E14" s="53" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F14" s="53" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="275.25" customHeight="1">
@@ -5801,17 +6176,17 @@
         <v>13</v>
       </c>
       <c r="B15" s="98" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C15" s="98"/>
       <c r="D15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E15" s="53" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F15" s="53" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="309" customHeight="1">
@@ -5819,15 +6194,15 @@
         <v>14</v>
       </c>
       <c r="B16" s="98" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C16" s="98"/>
       <c r="D16"/>
       <c r="E16" s="53" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F16" s="53" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="351.75" customHeight="1">
@@ -5835,15 +6210,15 @@
         <v>15</v>
       </c>
       <c r="B17" s="98" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C17" s="98"/>
       <c r="D17"/>
       <c r="E17" s="53" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F17" s="53" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="202.5" customHeight="1">
@@ -5851,17 +6226,17 @@
         <v>16</v>
       </c>
       <c r="B18" s="98" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C18" s="98"/>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E18" s="53" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F18" s="53" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="327" customHeight="1">
@@ -5869,15 +6244,15 @@
         <v>17</v>
       </c>
       <c r="B19" s="98" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C19" s="98"/>
       <c r="D19"/>
       <c r="E19" s="53" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F19" s="53" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="324" customHeight="1">
@@ -5885,15 +6260,15 @@
         <v>18</v>
       </c>
       <c r="B20" s="98" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C20" s="98"/>
       <c r="D20"/>
       <c r="E20" s="53" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F20" s="53" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="275.25" customHeight="1">
@@ -5901,17 +6276,17 @@
         <v>19</v>
       </c>
       <c r="B21" s="98" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C21" s="98"/>
       <c r="D21" s="48" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E21" s="53" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F21" s="53" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="381.75" customHeight="1">
@@ -5919,15 +6294,15 @@
         <v>20</v>
       </c>
       <c r="B22" s="98" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C22" s="98"/>
       <c r="D22" s="48"/>
       <c r="E22" s="53" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F22" s="53" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="381.75" customHeight="1">
@@ -5935,15 +6310,15 @@
         <v>21</v>
       </c>
       <c r="B23" s="98" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C23" s="98"/>
       <c r="D23" s="48"/>
       <c r="E23" s="53" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F23" s="53" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="134.25" customHeight="1">
@@ -5951,17 +6326,17 @@
         <v>22</v>
       </c>
       <c r="B24" s="102" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C24" s="102"/>
       <c r="D24" s="48" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E24" s="53" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F24" s="53" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="408" customHeight="1">
@@ -5969,12 +6344,12 @@
         <v>23</v>
       </c>
       <c r="B25" s="98" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C25" s="98"/>
       <c r="D25" s="48"/>
       <c r="E25" s="53" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F25" s="53"/>
     </row>
@@ -5983,12 +6358,12 @@
         <v>24</v>
       </c>
       <c r="B26" s="98" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C26" s="98"/>
       <c r="D26" s="48"/>
       <c r="E26" s="53" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F26" s="53"/>
     </row>
@@ -5997,17 +6372,17 @@
         <v>25</v>
       </c>
       <c r="B27" s="103" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C27" s="103"/>
       <c r="D27" s="48" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E27" s="53" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F27" s="53" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="240" customHeight="1">
@@ -6015,15 +6390,15 @@
         <v>26</v>
       </c>
       <c r="B28" s="98" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C28" s="98"/>
       <c r="D28" s="48"/>
       <c r="E28" s="53" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F28" s="53" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="213" customHeight="1">
@@ -6031,15 +6406,15 @@
         <v>27</v>
       </c>
       <c r="B29" s="98" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C29" s="98"/>
       <c r="D29" s="48"/>
       <c r="E29" s="53" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F29" s="53" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="170.25" customHeight="1">
@@ -6047,17 +6422,17 @@
         <v>28</v>
       </c>
       <c r="B30" s="102" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C30" s="102"/>
       <c r="D30" s="48" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E30" s="53" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F30" s="53" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="229.5" customHeight="1">
@@ -6065,15 +6440,15 @@
         <v>29</v>
       </c>
       <c r="B31" s="98" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C31" s="98"/>
       <c r="D31" s="48"/>
       <c r="E31" s="53" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F31" s="53" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="170.25" customHeight="1">
@@ -6081,15 +6456,15 @@
         <v>30</v>
       </c>
       <c r="B32" s="98" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C32" s="98"/>
       <c r="D32" s="48"/>
       <c r="E32" s="53" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F32" s="53" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="182.25" customHeight="1">
@@ -6097,15 +6472,15 @@
         <v>31</v>
       </c>
       <c r="B33" s="98" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C33" s="98"/>
       <c r="D33" s="48"/>
       <c r="E33" s="53" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F33" s="53" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="186" customHeight="1">
@@ -6113,15 +6488,15 @@
         <v>32</v>
       </c>
       <c r="B34" s="102" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C34" s="102"/>
       <c r="D34" s="48"/>
       <c r="E34" s="53" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F34" s="53" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="186" customHeight="1">
@@ -6129,17 +6504,17 @@
         <v>33</v>
       </c>
       <c r="B35" s="98" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C35" s="98"/>
       <c r="D35" s="48" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E35" s="53" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F35" s="53" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="186" customHeight="1">
@@ -6147,17 +6522,17 @@
         <v>34</v>
       </c>
       <c r="B36" s="98" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C36" s="98"/>
       <c r="D36" s="48" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E36" s="53" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F36" s="53" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="186" customHeight="1">
@@ -6165,17 +6540,17 @@
         <v>35</v>
       </c>
       <c r="B37" s="98" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C37" s="98"/>
       <c r="D37" s="48" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E37" s="53" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F37" s="53" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -6188,7 +6563,7 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="56" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B39" s="56"/>
       <c r="C39" s="56"/>
@@ -6198,7 +6573,7 @@
     </row>
     <row r="40" spans="1:6" ht="19.5" customHeight="1">
       <c r="A40" s="99" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B40" s="100"/>
       <c r="C40" s="100"/>
@@ -6211,19 +6586,19 @@
         <v>25</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F41" s="15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="42.75" customHeight="1">
@@ -6231,19 +6606,19 @@
         <v>10</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="27" customHeight="1">
@@ -6251,19 +6626,19 @@
         <v>10</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="24" customHeight="1">
@@ -6271,19 +6646,19 @@
         <v>10</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="38.25" customHeight="1">
@@ -6291,19 +6666,19 @@
         <v>10</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" spans="1:6" s="58" customFormat="1" ht="124.5" customHeight="1">
@@ -6311,19 +6686,19 @@
         <v>10</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="23.25" customHeight="1">
@@ -6331,19 +6706,19 @@
         <v>10</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -6351,19 +6726,19 @@
         <v>10</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -6371,19 +6746,19 @@
         <v>10</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -6391,19 +6766,19 @@
         <v>10</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -6411,19 +6786,19 @@
         <v>10</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -6431,19 +6806,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -6451,19 +6826,19 @@
         <v>10</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D53" s="23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -6471,19 +6846,19 @@
         <v>10</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D54" s="23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -6491,19 +6866,19 @@
         <v>10</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D55" s="23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -6511,19 +6886,19 @@
         <v>10</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D56" s="23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -6531,19 +6906,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -6551,19 +6926,19 @@
         <v>10</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="95.25" customHeight="1">
@@ -6571,19 +6946,19 @@
         <v>10</v>
       </c>
       <c r="B59" s="14" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D59" s="23" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -6591,16 +6966,16 @@
         <v>10</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D60" s="23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F60" s="14"/>
     </row>
@@ -6609,19 +6984,19 @@
         <v>10</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D61" s="23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="108" customHeight="1">
@@ -6629,19 +7004,19 @@
         <v>10</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D62" s="23" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="105" customHeight="1">
@@ -6649,19 +7024,19 @@
         <v>10</v>
       </c>
       <c r="B63" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="C63" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="D63" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="E63" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="F63" s="14" t="s">
         <v>210</v>
-      </c>
-      <c r="C63" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="D63" s="23" t="s">
-        <v>207</v>
-      </c>
-      <c r="E63" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="F63" s="14" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="111" customHeight="1">
@@ -6669,19 +7044,19 @@
         <v>10</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="99.75" customHeight="1">
@@ -6689,19 +7064,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E65" s="14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="103.5" customHeight="1">
@@ -6709,19 +7084,19 @@
         <v>10</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D66" s="23" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="106.5" customHeight="1">
@@ -6729,19 +7104,19 @@
         <v>10</v>
       </c>
       <c r="B67" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E67" s="14" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F67" s="14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="109.5" customHeight="1">
@@ -6749,19 +7124,19 @@
         <v>10</v>
       </c>
       <c r="B68" s="14" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D68" s="23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -6769,19 +7144,19 @@
         <v>10</v>
       </c>
       <c r="B69" s="14" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F69" s="14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -6789,19 +7164,19 @@
         <v>10</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F70" s="14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -6809,19 +7184,19 @@
         <v>10</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F71" s="14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -6829,17 +7204,17 @@
         <v>10</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E72" s="14"/>
       <c r="F72" s="14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -6903,7 +7278,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.75">
       <c r="A1" s="93" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B1" s="94"/>
       <c r="C1" s="94"/>
@@ -6913,19 +7288,19 @@
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1">
       <c r="A2" s="15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F2" s="25"/>
     </row>
@@ -6934,16 +7309,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F3" s="25"/>
     </row>
@@ -6952,16 +7327,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F4" s="25"/>
     </row>
@@ -6970,16 +7345,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F5" s="25"/>
     </row>
@@ -6988,16 +7363,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F6" s="25"/>
     </row>
@@ -7006,16 +7381,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F7" s="25"/>
     </row>
@@ -7029,7 +7404,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="33" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B9" s="33"/>
       <c r="C9" s="25"/>
@@ -7039,7 +7414,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="95" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B10" s="96"/>
       <c r="C10" s="96"/>
@@ -7052,19 +7427,19 @@
         <v>25</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -7072,19 +7447,19 @@
         <v>32</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D12" s="34">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F12" s="29" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -7092,19 +7467,19 @@
         <v>32</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D13" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E13" s="37" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F13" s="32" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -7112,19 +7487,19 @@
         <v>32</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F14" s="32" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -7132,19 +7507,19 @@
         <v>32</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D15" s="34">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E15" s="30" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F15" s="32" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -7152,19 +7527,19 @@
         <v>32</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D16" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E16" s="30" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F16" s="32" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -7172,19 +7547,19 @@
         <v>32</v>
       </c>
       <c r="B17" s="32" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E17" s="32" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F17" s="32" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -7192,19 +7567,19 @@
         <v>32</v>
       </c>
       <c r="B18" s="32" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D18" s="34">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F18" s="32" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -7212,19 +7587,19 @@
         <v>32</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D19" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F19" s="32" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -7232,19 +7607,19 @@
         <v>32</v>
       </c>
       <c r="B20" s="32" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C20" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D20" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F20" s="32" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -7252,19 +7627,19 @@
         <v>32</v>
       </c>
       <c r="B21" s="32" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D21" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E21" s="30" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F21" s="32" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -7272,19 +7647,19 @@
         <v>32</v>
       </c>
       <c r="B22" s="39" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D22" s="40">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E22" s="38" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -7292,19 +7667,19 @@
         <v>32</v>
       </c>
       <c r="B23" s="29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D23" s="41">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E23" s="29" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F23" s="29" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -7312,19 +7687,19 @@
         <v>32</v>
       </c>
       <c r="B24" s="32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C24" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D24" s="32" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E24" s="32" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F24" s="32" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -7332,19 +7707,19 @@
         <v>32</v>
       </c>
       <c r="B25" s="32" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D25" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F25" s="32" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -7352,19 +7727,19 @@
         <v>32</v>
       </c>
       <c r="B26" s="32" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C26" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D26" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E26" s="30" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F26" s="32" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -7372,19 +7747,19 @@
         <v>32</v>
       </c>
       <c r="B27" s="32" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C27" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D27" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E27" s="30" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F27" s="32" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -7392,19 +7767,19 @@
         <v>32</v>
       </c>
       <c r="B28" s="32" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C28" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D28" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E28" s="30" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F28" s="32" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -7412,19 +7787,19 @@
         <v>32</v>
       </c>
       <c r="B29" s="32" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C29" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D29" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E29" s="30" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F29" s="32" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -7432,19 +7807,19 @@
         <v>32</v>
       </c>
       <c r="B30" s="32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C30" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D30" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E30" s="30" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F30" s="32" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -7452,19 +7827,19 @@
         <v>32</v>
       </c>
       <c r="B31" s="32" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C31" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D31" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E31" s="30" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F31" s="32" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -7472,19 +7847,19 @@
         <v>32</v>
       </c>
       <c r="B32" s="32" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C32" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D32" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E32" s="30" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F32" s="32" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -7492,19 +7867,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="32" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D33" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E33" s="30" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F33" s="32" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -7512,19 +7887,19 @@
         <v>32</v>
       </c>
       <c r="B34" s="32" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C34" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D34" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F34" s="32" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -7532,19 +7907,19 @@
         <v>32</v>
       </c>
       <c r="B35" s="32" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C35" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D35" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E35" s="30" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F35" s="32" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -7552,19 +7927,19 @@
         <v>32</v>
       </c>
       <c r="B36" s="32" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C36" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D36" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E36" s="30" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F36" s="32" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -7572,19 +7947,19 @@
         <v>32</v>
       </c>
       <c r="B37" s="32" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C37" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D37" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E37" s="30" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F37" s="32" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -7592,19 +7967,19 @@
         <v>32</v>
       </c>
       <c r="B38" s="32" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C38" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D38" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E38" s="30" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F38" s="32" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -7612,19 +7987,19 @@
         <v>32</v>
       </c>
       <c r="B39" s="32" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C39" s="32" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D39" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E39" s="30" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F39" s="32" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -7632,19 +8007,19 @@
         <v>32</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C40" s="32" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D40" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E40" s="30" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F40" s="32" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -7652,19 +8027,19 @@
         <v>32</v>
       </c>
       <c r="B41" s="32" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C41" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D41" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E41" s="30" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F41" s="32" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -7672,19 +8047,19 @@
         <v>32</v>
       </c>
       <c r="B42" s="32" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C42" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D42" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E42" s="30" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F42" s="32" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -7692,19 +8067,19 @@
         <v>32</v>
       </c>
       <c r="B43" s="32" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C43" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D43" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F43" s="32" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -7712,19 +8087,19 @@
         <v>32</v>
       </c>
       <c r="B44" s="32" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C44" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D44" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E44" s="30" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F44" s="32" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -7732,19 +8107,19 @@
         <v>32</v>
       </c>
       <c r="B45" s="32" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C45" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E45" s="32" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F45" s="32" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -7752,19 +8127,19 @@
         <v>32</v>
       </c>
       <c r="B46" s="32" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C46" s="32" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D46" s="34">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E46" s="30" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F46" s="32" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -7772,19 +8147,19 @@
         <v>32</v>
       </c>
       <c r="B47" s="32" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C47" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D47" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E47" s="30" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F47" s="32" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -7792,19 +8167,19 @@
         <v>32</v>
       </c>
       <c r="B48" s="32" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C48" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D48" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E48" s="30" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F48" s="32" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -7812,19 +8187,19 @@
         <v>32</v>
       </c>
       <c r="B49" s="32" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C49" s="32" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D49" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E49" s="30" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F49" s="32" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -7832,19 +8207,19 @@
         <v>32</v>
       </c>
       <c r="B50" s="32" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C50" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D50" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E50" s="30" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F50" s="32" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -7852,19 +8227,19 @@
         <v>32</v>
       </c>
       <c r="B51" s="32" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C51" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D51" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E51" s="30" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F51" s="32" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -7872,19 +8247,19 @@
         <v>32</v>
       </c>
       <c r="B52" s="32" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C52" s="32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D52" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E52" s="37" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F52" s="32" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -7892,19 +8267,19 @@
         <v>32</v>
       </c>
       <c r="B53" s="32" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C53" s="32" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D53" s="36">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E53" s="37" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F53" s="32" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -7917,15 +8292,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
@@ -7935,7 +8301,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -8107,14 +8473,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFA63DCF-9520-4E04-9337-B32B74101E78}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED0C13A3-7E6E-461A-96D1-122E5E8A95BC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED0C13A3-7E6E-461A-96D1-122E5E8A95BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F9B6A3B-BED9-4FC8-B2D5-053C860D1113}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F9B6A3B-BED9-4FC8-B2D5-053C860D1113}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFA63DCF-9520-4E04-9337-B32B74101E78}"/>
 </file>
--- a/input/mapping/008. OCB_GOLD_TCKH_V_CUST_STATUS_BAOANH.xlsx
+++ b/input/mapping/008. OCB_GOLD_TCKH_V_CUST_STATUS_BAOANH.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/ANHPB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="406" documentId="13_ncr:1_{B6C0F684-96C5-4E16-9696-74D396B07D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD51B7AC-B97F-4FEE-BA11-E91ECF4FEA9D}"/>
+  <xr:revisionPtr revIDLastSave="495" documentId="13_ncr:1_{B6C0F684-96C5-4E16-9696-74D396B07D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1032D29A-AFF0-4899-ADEF-5FAA7E4E4B05}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{15579902-C16A-4DCC-801B-11A268672AD5}"/>
   </bookViews>
@@ -16,8 +16,8 @@
     <sheet name="Summary" sheetId="11" r:id="rId1"/>
     <sheet name="Script" sheetId="15" r:id="rId2"/>
     <sheet name="V_CUST_STATUS" sheetId="12" r:id="rId3"/>
-    <sheet name="CST_LCS_KT_30D_FINAL_CASE5" sheetId="17" r:id="rId4"/>
-    <sheet name="T24_CUSTOMER" sheetId="13" r:id="rId5"/>
+    <sheet name="T24_CUSTOMER" sheetId="13" r:id="rId4"/>
+    <sheet name="CST_LCS_KT_30D_FINAL_CASE5" sheetId="17" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028" iterateDelta="1E-4" calcOnSave="0"/>
   <extLst>
@@ -263,42 +263,8 @@
 </t>
   </si>
   <si>
-    <t>USE CATALOG IDENTIFIER(:curated);
+    <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE TABLE IF NOT EXISTS CST_LCS_KT_30D_FINAL_CASE5 (
-    DATA_DT                 DATE,
-    CIF                     DECIMAL(10,0),
-    T_COMPANY_BOOK          STRING,
-    T_CREATE_DATE           DATE NOT NULL,
-    FINAL_STATUS            STRING,
-    SCTR                    DECIMAL(10,0),
-    T_DESCRIPTION           STRING,
-    CST_GRP                 STRING,
-    CUST_GROUP_NAME         STRING,
-    CUST_GROUP_LINE         STRING,
-    CUST_GROUP_LINE_SHORT   STRING,
-    TIENGUI                 DECIMAL(20,4),
-    TIENVAY                 DECIMAL(20,4),
-    CUST_CURRENT_ACCT_A1    DECIMAL(20,4),
-    CIF_LOANCLASS            DECIMAL(3,0),
-    DOANHSO_BAOLANH_30D     DECIMAL(31,4),
-    DOANHSO_LC_30D          DECIMAL(31,4),
-    NUM_TRANS               INT,
-    ACTIVE_INDEX            INT,
-    T24_STATUS              STRING,
-    T24_ACTIVE_RB           INT,
-    T24_ACTIVE_COMB         INT,
-    T24_ACTIVE_TRE          INT,
-    T24_ACTIVE_CIB          INT,
-    T24_ACTIVE_CMB          INT,
-    T24_ACTIVE_DCTC         INT,
-    T24_ACTIVE_LIO          INT,
-    W4_STATUS               STRING,
-    W4_ACTIVE_RB            INT,
-    W4_ACTIVE_LIO           INT,
-    DATE_SYS                TIMESTAMP
-)
-USING DELTA;
 INSERT INTO CST_LCS_KT_30D_FINAL_CASE5
 REPLACE WHERE DATA_DT = to_date(:DATADT, 'yyyyMMdd')
 WITH
@@ -439,7 +405,7 @@
 cte_cust_group AS (
     SELECT
         ocg.ref_code,
-        max_by(ocg.ref_description, ocg.source_event_date) AS cust_group_name   -- cột 9
+        max_by(ocg.ref_description, ocg.source_event_date) AS cust_group_name  
     FROM IDENTIFIER(:cleaned || '.raw_vault.ref_t24_ocbh_cus_group') ocg
     WHERE ocg.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY ocg.ref_code
@@ -460,7 +426,7 @@
         max_by(ccb.so_du_bao_lanh, ccb.source_event_date) AS so_du_bao_lanh,
         max_by(ccb.so_du_lc,       ccb.source_event_date) AS so_du_lc
     FROM IDENTIFIER(:cleaned || '.business_vault.csat_customer_sum_balance') ccb
-    WHERE ccb.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+    WHERE ccb.source_event_date = to_date(:DATADT, 'yyyyMMdd')
     GROUP BY ccb.customer_hashkey
 ),
 cte_acct_base AS (   -- Bước 1
@@ -582,7 +548,7 @@
     LEFT JOIN cte_md_deal_sts_del d_md
       ON d_md.md_deal_hashkey = smdi.md_deal_hashkey
     WHERE smdi.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
-      AND smdi.t_value_date BETWEEN DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30) AND to_date(:DATADT, 'yyyyMMdd')
+      AND to_date(smdi.t_value_date, 'yyyyMMdd') BETWEEN DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30) AND to_date(:DATADT, 'yyyyMMdd')
       AND d_md.md_deal_hashkey IS NULL
     GROUP BY smdi.md_deal_hashkey
 ),
@@ -597,10 +563,13 @@
       ON hmd.md_deal_hashkey = md1.md_deal_hashkey
     JOIN cte_snap_hub_crb hcb
       ON hcb.tieukhoan = hmd.business_key AND hcb.gl &lt;&gt; '9995'
+    LEFT JOIN cte_crb_sts_del d_crb                                   
+      ON d_crb.crb_hashkey = hcb.crb_hashkey                         
     LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_crb_balance') scb
-      ON scb.crb_hashkey = hcb.crb_hashkey
-     AND scb.ma_key BETWEEN date_format(DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30), 'yyyyMMdd') AND :DATADT
-     AND scb.source_event_date = to_date(:DATADT, 'yyyyMMdd')
+    ON scb.crb_hashkey = hcb.crb_hashkey
+    AND to_date(scb.ma_key, 'yyyyMMdd') BETWEEN DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30) AND to_date(:DATADT, 'yyyyMMdd')
+    AND scb.source_event_date = to_date(:DATADT, 'yyyyMMdd')
+    WHERE d_crb.crb_hashkey IS NULL                                 
 ),
 cte_doanhso_baolanh_30d AS (  
     SELECT
@@ -617,7 +586,7 @@
         max_by(slct.t_issue_date, slct.source_event_date) AS t_issue_date
     FROM IDENTIFIER(:cleaned || '.raw_vault.sat_letter_of_credit_terms') slct
     WHERE slct.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
-      AND slct.t_issue_date BETWEEN date_format(DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30), 'yyyyMMdd') AND :DATADT
+    AND to_date(slct.t_issue_date, 'yyyyMMdd') BETWEEN DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30) AND to_date(:DATADT, 'yyyyMMdd')
     GROUP BY slct.letter_of_credit_hashkey
 ),
 cte_lc_value AS (  
@@ -668,7 +637,7 @@
     JOIN IDENTIFIER(:cleaned || '.raw_vault.ref_currency') rc
       ON rc.id = v.t_lc_currency
      AND v.issue_date = rc.data_date
-     AND rc.data_date BETWEEN date_format(DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30), 'yyyyMMdd') AND :DATADT
+     AND to_date(rc.data_date, 'yyyyMMdd') BETWEEN DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30) AND to_date(:DATADT, 'yyyyMMdd')
     JOIN cte_lc_customer cust
       ON cust.letter_of_credit_hashkey = v.letter_of_credit_hashkey
     GROUP BY cust.customer_hashkey
@@ -835,10 +804,10 @@
       ON c.customer_hashkey = s.customer_hashkey
 ),
 cte_prev_bsn_day AS (   
-    SELECT MAX(msr_prd_id) AS prev_bsn_day
+    SELECT MAX(to_date(msr_prd_id, 'yyyyMMdd')) AS prev_bsn_day
     FROM cte_snap_calendar
     WHERE bsn_day_f = 1
-      AND msr_prd_id &lt; to_date(:DATADT, 'yyyyMMdd')
+      AND to_date(msr_prd_id, 'yyyyMMdd') &lt; to_date(:DATADT, 'yyyyMMdd')
 ),
 cte_new_cust AS (  
     SELECT bc.customer_hashkey
@@ -931,10 +900,8 @@
     FROM IDENTIFIER(:cleaned || '.raw_vault.sat_acnt_contract_information')
     WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY acnt_contract_hashkey
-),</t>
-  </si>
-  <si>
-    <t>cte_w4_acnt_contract_type_cur AS (   
+),
+cte_w4_acnt_contract_type_cur AS (   
     SELECT
         acnt_contract_hashkey,
         max_by(con_cat,  source_event_date) AS con_cat,
@@ -943,7 +910,10 @@
     WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY acnt_contract_hashkey
 ),
-cte_w4_acnt_contract_branch_cur AS (
+</t>
+  </si>
+  <si>
+    <t>cte_w4_acnt_contract_branch_cur AS (
     SELECT
         acnt_contract_hashkey,
         max_by(branch_hashkey, source_event_date) AS branch_hashkey
@@ -1136,8 +1106,8 @@
                        BETWEEN DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -180) AND DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -31)
                  THEN 1 ELSE 0 END AS trans_31_120d,
             CASE WHEN to_date(base.last_trans_date, 'yyyyMMdd') &lt; DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -180)
-                  AND base.last_trans_date &gt; '19000101'
-                 THEN 1 ELSE 0 END AS trans_121d
+                AND to_date(base.last_trans_date, 'yyyyMMdd') &gt; to_date('19000101', 'yyyyMMdd')
+                THEN 1 ELSE 0 END AS trans_121d
         FROM cte_w4_card_contract base
         LEFT JOIN cte_w4_balance bl ON bl.issuing_hashkey = base.issuing_hashkey
         LEFT JOIN cte_w4_loan_class lcls ON lcls.so_hd = base.issuing_number
@@ -1261,63 +1231,12 @@
 ;</t>
   </si>
   <si>
-    <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
+    <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE TABLE IF NOT EXISTS T24_CUSTOMER (
-    IP_ID                   INT,
-    ID                      DECIMAL(10, 0),
-    DATA_DATE               STRING,
-    T_SHORT_NAME            STRING,
-    T_LANGUAGE              STRING,
-    T_CREATE_DATE           STRING,
-    T_EDUCATION_LEVEL       STRING,
-    T_JOB_TITLE             STRING,
-    T_OCCUPATION            STRING,
-    T_MARITAL_STATUS        STRING,
-    T_LABOUR_NUMBER         DECIMAL(6, 0),
-    T_GENDER                STRING,
-    T_BIRTH_INCORP_DATE     STRING,
-    T_RESIDENCE             STRING,
-    T_NATIONALITY           STRING,
-    T_ADDRESS               STRING,
-    T_TOWN_COUNTRY          STRING,
-    T_PROVINCE_1            STRING,
-    T_PHONE_1               STRING,
-    T_SMS_1                 STRING,
-    T_OFF_PHONE             STRING,
-    T_EMAIL_1               STRING,
-    T_PROVINCE_2            STRING,
-    T_TOWN_COUNTRY_2        STRING,
-    T_SMS_2                 STRING,
-    T_PHONE_2               STRING,
-    T_OFF_PHONE_2           STRING,
-    T_SECTOR                DECIMAL(4, 0),
-    T_INDUSTRY              DECIMAL(4, 0),
-    T_CUST_GROUP            STRING,
-    T_TAX_ID                STRING,
-    T_LEGAL_ID              STRING,
-    T_LEGAL_DOC_NAME        STRING,
-    T_CONTACT_DATE          STRING,
-    T_PROVINCE              DECIMAL(4, 0),
-    T_FAX_1                 STRING,
-    T_EMAIL_2               STRING,
-    T_NET_MONTHLY_IN        DECIMAL(20, 4),
-    T_TOTAL_PROPERTY        STRING,
-    T_TOTAL_INCOME          STRING,
-    T_COMPANY_BOOK          STRING,
-    T_ACCOUNT_OFFICER       DECIMAL(8, 0)
-)
-USING DELTA;
--- STEP 1: Xóa dữ liệu cũ theo ngày
--- -------------------------------------------------------
 DELETE FROM T24_CUSTOMER
 WHERE DATA_DATE = :DATADT;
--- -------------------------------------------------------
--- STEP 2: Nạp dữ liệu mới từ Raw Vault
--- -------------------------------------------------------
 INSERT INTO T24_CUSTOMER
 WITH
--- STS HUB: chỉ giữ key có trạng thái MỚI NHẤT (&lt;= :DATADT) = 'D'
 cust_sts_del AS (
     SELECT customer_hashkey
     FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_customer')
@@ -1325,7 +1244,6 @@
     GROUP BY customer_hashkey
     HAVING max_by(cdc_status, source_event_date) = 'D'
 ),
--- HUB active: hub CUSTOMER đã LOẠI key bị xóa (anti-join cust_sts_del)
 cust_active AS (
     SELECT
         h.customer_hashkey,
@@ -1337,7 +1255,6 @@
       AND h.source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
       AND h.record_source = 't24__t24_customer'
 ),
--- SAT: sat_customer_other — bản mới nhất &lt;= :DATADT, mỗi customer_hashkey
 cust_other AS (
     SELECT
         customer_hashkey,
@@ -1349,7 +1266,6 @@
     WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
     GROUP BY customer_hashkey
 ),
--- LINK: COMPANY_BOOK — link_customer_branch (con trỏ mới nhất &lt;= :DATADT) → hub_branch.business_key
 cust_branch_cur AS (
     SELECT
         customer_hashkey,
@@ -1366,7 +1282,6 @@
     JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_branch') hb
         ON l.branch_hashkey = hb.branch_hashkey
 ),
--- LINK: ACCOUNT_OFFICER — link_customer_dept_acct_officer_nvql (con trỏ mới nhất &lt;= :DATADT) → hub_acct_officer.business_key
 cust_officer_cur AS (
     SELECT
         customer_hashkey,
@@ -1387,7 +1302,6 @@
     hub.customer_hashkey                                           AS IP_ID,
     hub.business_key                                               AS ID,
     DATE_FORMAT(pit.snapshot_date, 'yyyyMMdd')                     AS DATA_DATE,
-    -- sat_customer_information
     si.short_name                                                  AS T_SHORT_NAME,
     si.language                                                    AS T_LANGUAGE,
     TO_CHAR(TO_DATE(si.create_date, 'yyyyMMdd'), 'yyyyMMdd')::VARCHAR(8)      AS T_CREATE_DATE,
@@ -1400,7 +1314,6 @@
     TO_CHAR(TO_DATE(si.birth_incorp_date, 'yyyyMMdd'), 'yyyyMMdd')::VARCHAR(8) AS T_BIRTH_INCORP_DATE,
     si.residence                                                   AS T_RESIDENCE,
     si.nationality                                                 AS T_NATIONALITY,
-    -- sat_customer_contact
     sc.address                                                     AS T_ADDRESS,
     sc.town_country                                                AS T_TOWN_COUNTRY,
     sc.province_1                                                  AS T_PROVINCE_1,
@@ -1413,26 +1326,20 @@
     sc.sms_2                                                       AS T_SMS_2,
     sc.phone_2                                                     AS T_PHONE_2,
     sc.off_phone_2                                                 AS T_OFF_PHONE_2,
-    -- sat_customer_classification
     scl.sector                                                     AS T_SECTOR,
     scl.industry                                                   AS T_INDUSTRY,
     scl.cust_group                                                 AS T_CUST_GROUP,
-    -- sat_customer_kyc
     sk.tax_id                                                      AS T_TAX_ID,
     sk.legal_id                                                    AS T_LEGAL_ID,
     sk.legal_doc_name                                              AS T_LEGAL_DOC_NAME,
-    -- sat_customer_other
     TO_CHAR(TO_DATE(so.contact_date, 'yyyyMMdd'), 'yyyyMMdd')::VARCHAR(8)      AS T_CONTACT_DATE,
     so.province                                                    AS T_PROVINCE,
     so.fax_1                                                       AS T_FAX_1,
     so.email_2                                                     AS T_EMAIL_2,
-    -- sat_customer_financial_statement
     sf.net_monthly_in                                              AS T_NET_MONTHLY_IN,
     sf.total_property                                              AS T_TOTAL_PROPERTY,
     sf.total_income                                                AS T_TOTAL_INCOME,
-    -- link_customer_branch → hub_branch.business_key
     cb.company_book                                                AS T_COMPANY_BOOK,
-    -- link_customer_dept_acct_officer_nvql → hub_acct_officer.business_key
     ao.account_officer                                             AS T_ACCOUNT_OFFICER
 FROM IDENTIFIER(:cleaned || '.business_vault.pit_customer') pit
 LEFT JOIN cust_active hub
@@ -1457,8 +1364,7 @@
 LEFT JOIN cust_branch cb
     ON cb.customer_hashkey = hub.customer_hashkey
 LEFT JOIN cust_officer ao
-    ON ao.customer_hashkey = hub.customer_hashkey;
-</t>
+    ON ao.customer_hashkey = hub.customer_hashkey;</t>
   </si>
   <si>
     <t>V_CUST_STATUS — VIEW
@@ -1561,6 +1467,418 @@
   </si>
   <si>
     <t>B.T_GENDER</t>
+  </si>
+  <si>
+    <t>LV1 — View/Table được JOIN trực tiếp trong LV0</t>
+  </si>
+  <si>
+    <t>ON Condition / Ghi chu</t>
+  </si>
+  <si>
+    <t>pit_customer</t>
+  </si>
+  <si>
+    <t>pit</t>
+  </si>
+  <si>
+    <t>FROM pit_customer
+where snapshot_date = [ETL_DATE]</t>
+  </si>
+  <si>
+    <t>hub_active AS (
+SELECT h.customer_hashkey, h.business_key, h.source_event_date
+FROM ocb_datavault_pilotcloud_cleaned.raw_vault.hub_customer h
+LEFT JOIN (
+SELECT customer_hashkey FROM (
+SELECT customer_hashkey, cdc_status,
+ROW_NUMBER() OVER (PARTITION BY customer_hashkey
+ORDER BY source_event_date DESC) AS rn
+FROM ocb_datavault_pilotcloud_cleaned.raw_vault.sts_hub_customer
+WHERE source_event_date &lt;= TO_DATE(:p_data_date,'yyyyMMdd')
+) t WHERE rn = 1 AND cdc_status = 'D'
+) sts ON h.customer_hashkey = sts.customer_hashkey
+WHERE sts.customer_hashkey IS NULL
+AND h.source_event_date &lt;= TO_DATE(:p_data_date,'yyyyMMdd')
+AND h.record_source = 't24__t24_customer'
+)</t>
+  </si>
+  <si>
+    <t>hub</t>
+  </si>
+  <si>
+    <t>ON pit.customer_hashkey = hub.customer_hashkey</t>
+  </si>
+  <si>
+    <t>sat_other AS (
+SELECT customer_hashkey, contact_date, province, fax_1, email_2
+FROM (
+SELECT *, ROW_NUMBER() OVER (PARTITION BY customer_hashkey
+ORDER BY source_event_date DESC) AS rn
+FROM ocb_datavault_pilotcloud_cleaned.raw_vault.sat_customer_other
+WHERE source_event_date &lt;= TO_DATE(:p_data_date,'yyyyMMdd')
+) t WHERE rn = 1
+)</t>
+  </si>
+  <si>
+    <t>so</t>
+  </si>
+  <si>
+    <t>ON hub.customer_hashkey = so.customer_hashkey</t>
+  </si>
+  <si>
+    <t>cust_branch AS (
+SELECT l.customer_hashkey, hb.business_key AS company_book
+FROM (
+SELECT customer_hashkey, branch_hashkey,
+ROW_NUMBER() OVER (PARTITION BY customer_hashkey
+ORDER BY source_event_date DESC) AS rn
+FROM ocb_datavault_pilotcloud_cleaned.raw_vault.link_customer_branch
+WHERE source_event_date &lt;= TO_DATE(:p_data_date,'yyyyMMdd')
+) l
+JOIN ocb_datavault_pilotcloud_cleaned.raw_vault.hub_branch hb
+ON l.branch_hashkey = hb.branch_hashkey
+WHERE l.rn = 1
+)</t>
+  </si>
+  <si>
+    <t>cb</t>
+  </si>
+  <si>
+    <t>ON hub.customer_hashkey = cb.customer_hashkey</t>
+  </si>
+  <si>
+    <t>cust_officer AS (
+SELECT l.customer_hashkey, ha.business_key AS account_officer
+FROM (
+SELECT customer_hashkey, dept_acct_officer_hashkey,
+ROW_NUMBER() OVER (PARTITION BY customer_hashkey
+ORDER BY source_event_date DESC) AS rn
+FROM ocb_datavault_pilotcloud_cleaned.raw_vault.link_customer_dept_acct_officer_nvql
+WHERE source_event_date &lt;= TO_DATE(:p_data_date,'yyyyMMdd')
+) l
+JOIN ocb_datavault_pilotcloud_cleaned.raw_vault.hub_acct_officer ha
+ON l.dept_acct_officer_hashkey = ha.dept_acct_officer_hashkey
+WHERE l.rn = 1
+)</t>
+  </si>
+  <si>
+    <t>ao</t>
+  </si>
+  <si>
+    <t>ON hub.customer_hashkey = ao.customer_hashkey</t>
+  </si>
+  <si>
+    <t>Note: Đây là bảng Snapshot Daily</t>
+  </si>
+  <si>
+    <t>FIELD MAPPING (T24_CUSTOMER)</t>
+  </si>
+  <si>
+    <t>DataType</t>
+  </si>
+  <si>
+    <t>Transform
+Type</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>IP_ID</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>hub.customer_hashkey</t>
+  </si>
+  <si>
+    <t>hub_customer</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>decimal(10, 0)</t>
+  </si>
+  <si>
+    <t>hub.business_key</t>
+  </si>
+  <si>
+    <t>DATA_DATE</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>Transform</t>
+  </si>
+  <si>
+    <t>pit.snapshot_date</t>
+  </si>
+  <si>
+    <t>T_SHORT_NAME</t>
+  </si>
+  <si>
+    <t>si.short_name</t>
+  </si>
+  <si>
+    <t>sat_customer_information</t>
+  </si>
+  <si>
+    <t>T_LANGUAGE</t>
+  </si>
+  <si>
+    <t>si.language</t>
+  </si>
+  <si>
+    <t>T_CREATE_DATE</t>
+  </si>
+  <si>
+    <t>TO_CHAR(TO_DATE(si.create_date, 'yyyyMMdd'), 'yyyyMMdd')::VARCHAR(8)</t>
+  </si>
+  <si>
+    <t>T_EDUCATION_LEVEL</t>
+  </si>
+  <si>
+    <t>si.education_level</t>
+  </si>
+  <si>
+    <t>T_JOB_TITLE</t>
+  </si>
+  <si>
+    <t>si.job_title</t>
+  </si>
+  <si>
+    <t>T_OCCUPATION</t>
+  </si>
+  <si>
+    <t>si.occupation</t>
+  </si>
+  <si>
+    <t>T_MARITAL_STATUS</t>
+  </si>
+  <si>
+    <t>si.marital_status</t>
+  </si>
+  <si>
+    <t>T_LABOUR_NUMBER</t>
+  </si>
+  <si>
+    <t>decimal(6, 0)</t>
+  </si>
+  <si>
+    <t>si.labour_number</t>
+  </si>
+  <si>
+    <t>si.gender</t>
+  </si>
+  <si>
+    <t>TO_CHAR(TO_DATE(si.birth_incorp_date, 'yyyyMMdd'), 'yyyyMMdd')::VARCHAR(8)</t>
+  </si>
+  <si>
+    <t>T_RESIDENCE</t>
+  </si>
+  <si>
+    <t>si.residence</t>
+  </si>
+  <si>
+    <t>T_NATIONALITY</t>
+  </si>
+  <si>
+    <t>si.nationality</t>
+  </si>
+  <si>
+    <t>T_ADDRESS</t>
+  </si>
+  <si>
+    <t>sc.address</t>
+  </si>
+  <si>
+    <t>sat_customer_contact</t>
+  </si>
+  <si>
+    <t>T_TOWN_COUNTRY</t>
+  </si>
+  <si>
+    <t>sc.town_country</t>
+  </si>
+  <si>
+    <t>T_PROVINCE_1</t>
+  </si>
+  <si>
+    <t>sc.province_1</t>
+  </si>
+  <si>
+    <t>T_PHONE_1</t>
+  </si>
+  <si>
+    <t>sc.phone_1</t>
+  </si>
+  <si>
+    <t>T_SMS_1</t>
+  </si>
+  <si>
+    <t>sc.sms_1</t>
+  </si>
+  <si>
+    <t>T_OFF_PHONE</t>
+  </si>
+  <si>
+    <t>sc.off_phone</t>
+  </si>
+  <si>
+    <t>T_EMAIL_1</t>
+  </si>
+  <si>
+    <t>sc.email_1</t>
+  </si>
+  <si>
+    <t>T_PROVINCE_2</t>
+  </si>
+  <si>
+    <t>sc.province_2</t>
+  </si>
+  <si>
+    <t>T_TOWN_COUNTRY_2</t>
+  </si>
+  <si>
+    <t>sc.town_country_2</t>
+  </si>
+  <si>
+    <t>T_SMS_2</t>
+  </si>
+  <si>
+    <t>sc.sms_2</t>
+  </si>
+  <si>
+    <t>T_PHONE_2</t>
+  </si>
+  <si>
+    <t>sc.phone_2</t>
+  </si>
+  <si>
+    <t>T_OFF_PHONE_2</t>
+  </si>
+  <si>
+    <t>sc.off_phone_2</t>
+  </si>
+  <si>
+    <t>T_SECTOR</t>
+  </si>
+  <si>
+    <t>decimal(4, 0)</t>
+  </si>
+  <si>
+    <t>scl.sector</t>
+  </si>
+  <si>
+    <t>sat_customer_classification</t>
+  </si>
+  <si>
+    <t>T_INDUSTRY</t>
+  </si>
+  <si>
+    <t>scl.industry</t>
+  </si>
+  <si>
+    <t>T_CUST_GROUP</t>
+  </si>
+  <si>
+    <t>scl.cust_group</t>
+  </si>
+  <si>
+    <t>T_TAX_ID</t>
+  </si>
+  <si>
+    <t>sk.tax_id</t>
+  </si>
+  <si>
+    <t>sat_customer_kyc</t>
+  </si>
+  <si>
+    <t>T_LEGAL_ID</t>
+  </si>
+  <si>
+    <t>sk.legal_id</t>
+  </si>
+  <si>
+    <t>T_LEGAL_DOC_NAME</t>
+  </si>
+  <si>
+    <t>sk.legal_doc_name</t>
+  </si>
+  <si>
+    <t>T_CONTACT_DATE</t>
+  </si>
+  <si>
+    <t>TO_CHAR(TO_DATE(so.contact_date, 'yyyyMMdd'), 'yyyyMMdd')::VARCHAR(8)</t>
+  </si>
+  <si>
+    <t>sat_customer_other</t>
+  </si>
+  <si>
+    <t>T_PROVINCE</t>
+  </si>
+  <si>
+    <t>so.province</t>
+  </si>
+  <si>
+    <t>T_FAX_1</t>
+  </si>
+  <si>
+    <t>so.fax_1</t>
+  </si>
+  <si>
+    <t>T_EMAIL_2</t>
+  </si>
+  <si>
+    <t>so.email_2</t>
+  </si>
+  <si>
+    <t>T_NET_MONTHLY_IN</t>
+  </si>
+  <si>
+    <t>decimal(20, 4)</t>
+  </si>
+  <si>
+    <t>sf.net_monthly_in</t>
+  </si>
+  <si>
+    <t>sat_customer_financial_statement</t>
+  </si>
+  <si>
+    <t>T_TOTAL_PROPERTY</t>
+  </si>
+  <si>
+    <t>sf.total_property</t>
+  </si>
+  <si>
+    <t>T_TOTAL_INCOME</t>
+  </si>
+  <si>
+    <t>sf.total_income</t>
+  </si>
+  <si>
+    <t>T_COMPANY_BOOK</t>
+  </si>
+  <si>
+    <t>cb.company_book</t>
+  </si>
+  <si>
+    <t>hub_branch</t>
+  </si>
+  <si>
+    <t>T_ACCOUNT_OFFICER</t>
+  </si>
+  <si>
+    <t>decimal(8, 0)</t>
+  </si>
+  <si>
+    <t>ao.account_officer</t>
+  </si>
+  <si>
+    <t>hub_acct_officer</t>
   </si>
   <si>
     <t>TMP_CST_LCS_KT_30D_FINAL_CASE5 — TABLE 
@@ -3033,9 +3351,6 @@
     <t>DATE</t>
   </si>
   <si>
-    <t>Transform</t>
-  </si>
-  <si>
     <t>TO_DATE(:p_data_date, 'yyyyMMdd')</t>
   </si>
   <si>
@@ -3048,16 +3363,10 @@
     <t>CAST(hc.business_key AS DECIMAL(10,0))</t>
   </si>
   <si>
-    <t>T_COMPANY_BOOK</t>
-  </si>
-  <si>
     <t>STRING</t>
   </si>
   <si>
     <t>hb.business_key</t>
-  </si>
-  <si>
-    <t>T_CREATE_DATE</t>
   </si>
   <si>
     <t>COALESCE(TO_DATE(sci.create_date,'yyyyMMdd'), CAST(hc.source_event_date AS DATE))</t>
@@ -3093,9 +3402,6 @@
     <t>CST_GRP</t>
   </si>
   <si>
-    <t>scl.cust_group</t>
-  </si>
-  <si>
     <t>CUST_GROUP_NAME</t>
   </si>
   <si>
@@ -3298,406 +3604,6 @@
   </si>
   <si>
     <t>N/A</t>
-  </si>
-  <si>
-    <t>LV1 — View/Table được JOIN trực tiếp trong LV0</t>
-  </si>
-  <si>
-    <t>ON Condition / Ghi chu</t>
-  </si>
-  <si>
-    <t>pit_customer</t>
-  </si>
-  <si>
-    <t>pit</t>
-  </si>
-  <si>
-    <t>FROM pit_customer
-where snapshot_date = [ETL_DATE]</t>
-  </si>
-  <si>
-    <t>hub_active AS (
-SELECT h.customer_hashkey, h.business_key, h.source_event_date
-FROM ocb_datavault_pilotcloud_cleaned.raw_vault.hub_customer h
-LEFT JOIN (
-SELECT customer_hashkey FROM (
-SELECT customer_hashkey, cdc_status,
-ROW_NUMBER() OVER (PARTITION BY customer_hashkey
-ORDER BY source_event_date DESC) AS rn
-FROM ocb_datavault_pilotcloud_cleaned.raw_vault.sts_hub_customer
-WHERE source_event_date &lt;= TO_DATE(:p_data_date,'yyyyMMdd')
-) t WHERE rn = 1 AND cdc_status = 'D'
-) sts ON h.customer_hashkey = sts.customer_hashkey
-WHERE sts.customer_hashkey IS NULL
-AND h.source_event_date &lt;= TO_DATE(:p_data_date,'yyyyMMdd')
-AND h.record_source = 't24__t24_customer'
-)</t>
-  </si>
-  <si>
-    <t>hub</t>
-  </si>
-  <si>
-    <t>ON pit.customer_hashkey = hub.customer_hashkey</t>
-  </si>
-  <si>
-    <t>sat_other AS (
-SELECT customer_hashkey, contact_date, province, fax_1, email_2
-FROM (
-SELECT *, ROW_NUMBER() OVER (PARTITION BY customer_hashkey
-ORDER BY source_event_date DESC) AS rn
-FROM ocb_datavault_pilotcloud_cleaned.raw_vault.sat_customer_other
-WHERE source_event_date &lt;= TO_DATE(:p_data_date,'yyyyMMdd')
-) t WHERE rn = 1
-)</t>
-  </si>
-  <si>
-    <t>so</t>
-  </si>
-  <si>
-    <t>ON hub.customer_hashkey = so.customer_hashkey</t>
-  </si>
-  <si>
-    <t>cust_branch AS (
-SELECT l.customer_hashkey, hb.business_key AS company_book
-FROM (
-SELECT customer_hashkey, branch_hashkey,
-ROW_NUMBER() OVER (PARTITION BY customer_hashkey
-ORDER BY source_event_date DESC) AS rn
-FROM ocb_datavault_pilotcloud_cleaned.raw_vault.link_customer_branch
-WHERE source_event_date &lt;= TO_DATE(:p_data_date,'yyyyMMdd')
-) l
-JOIN ocb_datavault_pilotcloud_cleaned.raw_vault.hub_branch hb
-ON l.branch_hashkey = hb.branch_hashkey
-WHERE l.rn = 1
-)</t>
-  </si>
-  <si>
-    <t>cb</t>
-  </si>
-  <si>
-    <t>ON hub.customer_hashkey = cb.customer_hashkey</t>
-  </si>
-  <si>
-    <t>cust_officer AS (
-SELECT l.customer_hashkey, ha.business_key AS account_officer
-FROM (
-SELECT customer_hashkey, dept_acct_officer_hashkey,
-ROW_NUMBER() OVER (PARTITION BY customer_hashkey
-ORDER BY source_event_date DESC) AS rn
-FROM ocb_datavault_pilotcloud_cleaned.raw_vault.link_customer_dept_acct_officer_nvql
-WHERE source_event_date &lt;= TO_DATE(:p_data_date,'yyyyMMdd')
-) l
-JOIN ocb_datavault_pilotcloud_cleaned.raw_vault.hub_acct_officer ha
-ON l.dept_acct_officer_hashkey = ha.dept_acct_officer_hashkey
-WHERE l.rn = 1
-)</t>
-  </si>
-  <si>
-    <t>ao</t>
-  </si>
-  <si>
-    <t>ON hub.customer_hashkey = ao.customer_hashkey</t>
-  </si>
-  <si>
-    <t>Note: Đây là bảng Snapshot Daily</t>
-  </si>
-  <si>
-    <t>FIELD MAPPING (T24_CUSTOMER)</t>
-  </si>
-  <si>
-    <t>DataType</t>
-  </si>
-  <si>
-    <t>Transform
-Type</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>IP_ID</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>hub.customer_hashkey</t>
-  </si>
-  <si>
-    <t>hub_customer</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>decimal(10, 0)</t>
-  </si>
-  <si>
-    <t>hub.business_key</t>
-  </si>
-  <si>
-    <t>DATA_DATE</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>pit.snapshot_date</t>
-  </si>
-  <si>
-    <t>T_SHORT_NAME</t>
-  </si>
-  <si>
-    <t>si.short_name</t>
-  </si>
-  <si>
-    <t>sat_customer_information</t>
-  </si>
-  <si>
-    <t>T_LANGUAGE</t>
-  </si>
-  <si>
-    <t>si.language</t>
-  </si>
-  <si>
-    <t>TO_CHAR(TO_DATE(si.create_date, 'yyyyMMdd'), 'yyyyMMdd')::VARCHAR(8)</t>
-  </si>
-  <si>
-    <t>T_EDUCATION_LEVEL</t>
-  </si>
-  <si>
-    <t>si.education_level</t>
-  </si>
-  <si>
-    <t>T_JOB_TITLE</t>
-  </si>
-  <si>
-    <t>si.job_title</t>
-  </si>
-  <si>
-    <t>T_OCCUPATION</t>
-  </si>
-  <si>
-    <t>si.occupation</t>
-  </si>
-  <si>
-    <t>T_MARITAL_STATUS</t>
-  </si>
-  <si>
-    <t>si.marital_status</t>
-  </si>
-  <si>
-    <t>T_LABOUR_NUMBER</t>
-  </si>
-  <si>
-    <t>decimal(6, 0)</t>
-  </si>
-  <si>
-    <t>si.labour_number</t>
-  </si>
-  <si>
-    <t>si.gender</t>
-  </si>
-  <si>
-    <t>TO_CHAR(TO_DATE(si.birth_incorp_date, 'yyyyMMdd'), 'yyyyMMdd')::VARCHAR(8)</t>
-  </si>
-  <si>
-    <t>T_RESIDENCE</t>
-  </si>
-  <si>
-    <t>si.residence</t>
-  </si>
-  <si>
-    <t>T_NATIONALITY</t>
-  </si>
-  <si>
-    <t>si.nationality</t>
-  </si>
-  <si>
-    <t>T_ADDRESS</t>
-  </si>
-  <si>
-    <t>sc.address</t>
-  </si>
-  <si>
-    <t>sat_customer_contact</t>
-  </si>
-  <si>
-    <t>T_TOWN_COUNTRY</t>
-  </si>
-  <si>
-    <t>sc.town_country</t>
-  </si>
-  <si>
-    <t>T_PROVINCE_1</t>
-  </si>
-  <si>
-    <t>sc.province_1</t>
-  </si>
-  <si>
-    <t>T_PHONE_1</t>
-  </si>
-  <si>
-    <t>sc.phone_1</t>
-  </si>
-  <si>
-    <t>T_SMS_1</t>
-  </si>
-  <si>
-    <t>sc.sms_1</t>
-  </si>
-  <si>
-    <t>T_OFF_PHONE</t>
-  </si>
-  <si>
-    <t>sc.off_phone</t>
-  </si>
-  <si>
-    <t>T_EMAIL_1</t>
-  </si>
-  <si>
-    <t>sc.email_1</t>
-  </si>
-  <si>
-    <t>T_PROVINCE_2</t>
-  </si>
-  <si>
-    <t>sc.province_2</t>
-  </si>
-  <si>
-    <t>T_TOWN_COUNTRY_2</t>
-  </si>
-  <si>
-    <t>sc.town_country_2</t>
-  </si>
-  <si>
-    <t>T_SMS_2</t>
-  </si>
-  <si>
-    <t>sc.sms_2</t>
-  </si>
-  <si>
-    <t>T_PHONE_2</t>
-  </si>
-  <si>
-    <t>sc.phone_2</t>
-  </si>
-  <si>
-    <t>T_OFF_PHONE_2</t>
-  </si>
-  <si>
-    <t>sc.off_phone_2</t>
-  </si>
-  <si>
-    <t>T_SECTOR</t>
-  </si>
-  <si>
-    <t>decimal(4, 0)</t>
-  </si>
-  <si>
-    <t>scl.sector</t>
-  </si>
-  <si>
-    <t>sat_customer_classification</t>
-  </si>
-  <si>
-    <t>T_INDUSTRY</t>
-  </si>
-  <si>
-    <t>scl.industry</t>
-  </si>
-  <si>
-    <t>T_CUST_GROUP</t>
-  </si>
-  <si>
-    <t>T_TAX_ID</t>
-  </si>
-  <si>
-    <t>sk.tax_id</t>
-  </si>
-  <si>
-    <t>sat_customer_kyc</t>
-  </si>
-  <si>
-    <t>T_LEGAL_ID</t>
-  </si>
-  <si>
-    <t>sk.legal_id</t>
-  </si>
-  <si>
-    <t>T_LEGAL_DOC_NAME</t>
-  </si>
-  <si>
-    <t>sk.legal_doc_name</t>
-  </si>
-  <si>
-    <t>T_CONTACT_DATE</t>
-  </si>
-  <si>
-    <t>TO_CHAR(TO_DATE(so.contact_date, 'yyyyMMdd'), 'yyyyMMdd')::VARCHAR(8)</t>
-  </si>
-  <si>
-    <t>sat_customer_other</t>
-  </si>
-  <si>
-    <t>T_PROVINCE</t>
-  </si>
-  <si>
-    <t>so.province</t>
-  </si>
-  <si>
-    <t>T_FAX_1</t>
-  </si>
-  <si>
-    <t>so.fax_1</t>
-  </si>
-  <si>
-    <t>T_EMAIL_2</t>
-  </si>
-  <si>
-    <t>so.email_2</t>
-  </si>
-  <si>
-    <t>T_NET_MONTHLY_IN</t>
-  </si>
-  <si>
-    <t>decimal(20, 4)</t>
-  </si>
-  <si>
-    <t>sf.net_monthly_in</t>
-  </si>
-  <si>
-    <t>sat_customer_financial_statement</t>
-  </si>
-  <si>
-    <t>T_TOTAL_PROPERTY</t>
-  </si>
-  <si>
-    <t>sf.total_property</t>
-  </si>
-  <si>
-    <t>T_TOTAL_INCOME</t>
-  </si>
-  <si>
-    <t>sf.total_income</t>
-  </si>
-  <si>
-    <t>cb.company_book</t>
-  </si>
-  <si>
-    <t>hub_branch</t>
-  </si>
-  <si>
-    <t>T_ACCOUNT_OFFICER</t>
-  </si>
-  <si>
-    <t>decimal(8, 0)</t>
-  </si>
-  <si>
-    <t>ao.account_officer</t>
-  </si>
-  <si>
-    <t>hub_acct_officer</t>
   </si>
 </sst>
 </file>
@@ -5595,7 +5501,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0BC621D-40BB-4371-8CAF-4175E066EA14}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="11"/>
@@ -5604,7 +5510,7 @@
     <col min="4" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" thickBot="1">
+    <row r="1" spans="1:4" ht="15.75" thickBot="1">
       <c r="A1" s="42" t="s">
         <v>24</v>
       </c>
@@ -5618,7 +5524,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="21" customHeight="1">
+    <row r="2" spans="1:4" ht="21" customHeight="1">
       <c r="A2" s="11" t="s">
         <v>28</v>
       </c>
@@ -5629,7 +5535,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:4">
       <c r="A3" s="11" t="s">
         <v>28</v>
       </c>
@@ -5643,7 +5549,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:4">
       <c r="A4" s="11" t="s">
         <v>28</v>
       </c>
@@ -5654,7 +5560,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:4">
       <c r="A5" s="11" t="s">
         <v>34</v>
       </c>
@@ -5665,7 +5571,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:4">
       <c r="A6" s="11" t="s">
         <v>34</v>
       </c>
@@ -5676,7 +5582,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:4">
       <c r="A7" s="11" t="s">
         <v>34</v>
       </c>
@@ -5686,9 +5592,8 @@
       <c r="C7" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="F7"/>
-    </row>
-    <row r="8" spans="1:6">
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="11" t="s">
         <v>34</v>
       </c>
@@ -5932,6 +5837,1035 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59F34768-8776-4561-AACB-12FF947975B8}">
+  <dimension ref="A1:F53"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17.140625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="55.28515625" style="26" customWidth="1"/>
+    <col min="3" max="3" width="24.85546875" style="26" customWidth="1"/>
+    <col min="4" max="4" width="36.7109375" style="26" customWidth="1"/>
+    <col min="5" max="5" width="46" style="26" customWidth="1"/>
+    <col min="6" max="6" width="32.85546875" style="26" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="26"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.75">
+      <c r="A1" s="93" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="25"/>
+    </row>
+    <row r="2" spans="1:6" ht="18.75" customHeight="1">
+      <c r="A2" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="25"/>
+    </row>
+    <row r="3" spans="1:6" ht="30">
+      <c r="A3" s="27">
+        <v>1</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="F3" s="25"/>
+    </row>
+    <row r="4" spans="1:6" ht="345">
+      <c r="A4" s="30">
+        <v>2</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" s="25"/>
+    </row>
+    <row r="5" spans="1:6" ht="210">
+      <c r="A5" s="30">
+        <v>3</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F5" s="25"/>
+    </row>
+    <row r="6" spans="1:6" ht="285">
+      <c r="A6" s="30">
+        <v>4</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="F6" s="25"/>
+    </row>
+    <row r="7" spans="1:6" ht="300">
+      <c r="A7" s="30">
+        <v>5</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="F7" s="25"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" s="33"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="95" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="96"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="97"/>
+      <c r="F10" s="17"/>
+    </row>
+    <row r="11" spans="1:6" ht="23.25" customHeight="1">
+      <c r="A11" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" s="34">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E12" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E13" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="E14" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="F14" s="32" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D15" s="34">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D16" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D17" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="E17" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="F17" s="32" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" s="34">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="F18" s="32" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="F19" s="32" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E20" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E21" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="F21" s="32" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="C22" s="39" t="s">
+        <v>120</v>
+      </c>
+      <c r="D22" s="40">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E22" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="F22" s="39" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" s="41">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E23" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="F23" s="29" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D24" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="E24" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="F24" s="32" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="C25" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E25" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="F25" s="32" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E26" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="F26" s="32" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="C27" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D27" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E27" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="F27" s="32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="C28" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D28" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E28" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="F28" s="32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D29" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E29" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="F29" s="32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="C30" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D30" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E30" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="F30" s="32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="C31" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D31" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E31" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="F31" s="32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="C32" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D32" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E32" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="F32" s="32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="32" t="s">
+        <v>141</v>
+      </c>
+      <c r="C33" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E33" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="F33" s="32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="32" t="s">
+        <v>143</v>
+      </c>
+      <c r="C34" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D34" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E34" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="F34" s="32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="C35" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D35" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E35" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="F35" s="32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="C36" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D36" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E36" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="F36" s="32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="C37" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D37" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E37" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="F37" s="32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B38" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="C38" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D38" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E38" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="F38" s="32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B39" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="C39" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="D39" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E39" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="F39" s="32" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B40" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="C40" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="D40" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E40" s="30" t="s">
+        <v>158</v>
+      </c>
+      <c r="F40" s="32" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B41" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="C41" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D41" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E41" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="F41" s="32" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B42" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="C42" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D42" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E42" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="F42" s="32" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B43" s="32" t="s">
+        <v>164</v>
+      </c>
+      <c r="C43" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D43" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E43" s="30" t="s">
+        <v>165</v>
+      </c>
+      <c r="F43" s="32" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B44" s="32" t="s">
+        <v>166</v>
+      </c>
+      <c r="C44" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D44" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E44" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="F44" s="32" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="C45" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D45" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="E45" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="F45" s="32" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B46" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="C46" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="D46" s="34">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E46" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="F46" s="32" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B47" s="32" t="s">
+        <v>173</v>
+      </c>
+      <c r="C47" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D47" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E47" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="F47" s="32" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B48" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="C48" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D48" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E48" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="F48" s="32" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B49" s="32" t="s">
+        <v>177</v>
+      </c>
+      <c r="C49" s="32" t="s">
+        <v>178</v>
+      </c>
+      <c r="D49" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E49" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="F49" s="32" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B50" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="C50" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D50" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E50" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="F50" s="32" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B51" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="C51" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D51" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E51" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="F51" s="32" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B52" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="C52" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D52" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E52" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="F52" s="32" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B53" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="C53" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="D53" s="36">
+        <v>4.2361111111111113E-2</v>
+      </c>
+      <c r="E53" s="37" t="s">
+        <v>190</v>
+      </c>
+      <c r="F53" s="32" t="s">
+        <v>191</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{530181AD-2328-44FE-8AC6-F75E83D3A961}">
   <dimension ref="A1:F72"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
@@ -5947,7 +6881,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="51" customHeight="1">
       <c r="A1" s="106" t="s">
-        <v>71</v>
+        <v>192</v>
       </c>
       <c r="B1" s="69"/>
       <c r="C1" s="69"/>
@@ -5978,17 +6912,17 @@
         <v>1</v>
       </c>
       <c r="B3" s="107" t="s">
-        <v>72</v>
+        <v>193</v>
       </c>
       <c r="C3" s="108"/>
       <c r="D3" s="46" t="s">
-        <v>73</v>
+        <v>194</v>
       </c>
       <c r="E3" s="47" t="s">
         <v>46</v>
       </c>
       <c r="F3" s="47" t="s">
-        <v>74</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="153.75" customHeight="1">
@@ -5996,14 +6930,14 @@
         <v>2</v>
       </c>
       <c r="B4" s="102" t="s">
-        <v>75</v>
+        <v>196</v>
       </c>
       <c r="C4" s="102"/>
       <c r="D4" s="52" t="s">
-        <v>76</v>
+        <v>197</v>
       </c>
       <c r="E4" s="53" t="s">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="F4" s="53"/>
     </row>
@@ -6012,14 +6946,14 @@
         <v>3</v>
       </c>
       <c r="B5" s="109" t="s">
-        <v>78</v>
+        <v>199</v>
       </c>
       <c r="C5" s="110"/>
       <c r="D5" s="52" t="s">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="E5" s="53" t="s">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="F5" s="53"/>
     </row>
@@ -6028,17 +6962,17 @@
         <v>4</v>
       </c>
       <c r="B6" s="104" t="s">
-        <v>80</v>
+        <v>201</v>
       </c>
       <c r="C6" s="104"/>
       <c r="D6" s="52" t="s">
-        <v>81</v>
+        <v>202</v>
       </c>
       <c r="E6" s="53" t="s">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="F6" s="53" t="s">
-        <v>82</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="113.25" customHeight="1">
@@ -6046,14 +6980,14 @@
         <v>5</v>
       </c>
       <c r="B7" s="104" t="s">
-        <v>83</v>
+        <v>204</v>
       </c>
       <c r="C7" s="104"/>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>205</v>
       </c>
       <c r="E7" s="53" t="s">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="F7" s="53"/>
     </row>
@@ -6062,14 +6996,14 @@
         <v>6</v>
       </c>
       <c r="B8" s="105" t="s">
-        <v>85</v>
+        <v>206</v>
       </c>
       <c r="C8" s="105"/>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>207</v>
       </c>
       <c r="E8" s="53" t="s">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="F8" s="53"/>
     </row>
@@ -6078,14 +7012,14 @@
         <v>7</v>
       </c>
       <c r="B9" s="102" t="s">
-        <v>87</v>
+        <v>208</v>
       </c>
       <c r="C9" s="102"/>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>209</v>
       </c>
       <c r="E9" s="53" t="s">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="F9" s="53"/>
     </row>
@@ -6094,15 +7028,15 @@
         <v>8</v>
       </c>
       <c r="B10" s="98" t="s">
-        <v>89</v>
+        <v>210</v>
       </c>
       <c r="C10" s="98"/>
       <c r="D10" s="54"/>
       <c r="E10" s="53" t="s">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="F10" s="53" t="s">
-        <v>91</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="408.75" customHeight="1">
@@ -6110,15 +7044,15 @@
         <v>9</v>
       </c>
       <c r="B11" s="98" t="s">
-        <v>92</v>
+        <v>213</v>
       </c>
       <c r="C11" s="98"/>
       <c r="D11"/>
       <c r="E11" s="53" t="s">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>93</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="105" customHeight="1">
@@ -6126,15 +7060,15 @@
         <v>10</v>
       </c>
       <c r="B12" s="102" t="s">
-        <v>94</v>
+        <v>215</v>
       </c>
       <c r="C12" s="102"/>
       <c r="D12"/>
       <c r="E12" s="53" t="s">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="F12" s="53" t="s">
-        <v>95</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="156.75" customHeight="1">
@@ -6142,15 +7076,15 @@
         <v>11</v>
       </c>
       <c r="B13" s="102" t="s">
-        <v>96</v>
+        <v>217</v>
       </c>
       <c r="C13" s="102"/>
       <c r="D13"/>
       <c r="E13" s="53" t="s">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="F13" s="53" t="s">
-        <v>97</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="118.5" customHeight="1">
@@ -6158,17 +7092,17 @@
         <v>12</v>
       </c>
       <c r="B14" s="98" t="s">
-        <v>98</v>
+        <v>219</v>
       </c>
       <c r="C14" s="98"/>
       <c r="D14" t="s">
-        <v>99</v>
+        <v>220</v>
       </c>
       <c r="E14" s="53" t="s">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="F14" s="53" t="s">
-        <v>100</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="275.25" customHeight="1">
@@ -6176,17 +7110,17 @@
         <v>13</v>
       </c>
       <c r="B15" s="98" t="s">
-        <v>101</v>
+        <v>222</v>
       </c>
       <c r="C15" s="98"/>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>223</v>
       </c>
       <c r="E15" s="53" t="s">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="F15" s="53" t="s">
-        <v>103</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="309" customHeight="1">
@@ -6194,15 +7128,15 @@
         <v>14</v>
       </c>
       <c r="B16" s="98" t="s">
-        <v>104</v>
+        <v>225</v>
       </c>
       <c r="C16" s="98"/>
       <c r="D16"/>
       <c r="E16" s="53" t="s">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="F16" s="53" t="s">
-        <v>105</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="351.75" customHeight="1">
@@ -6210,15 +7144,15 @@
         <v>15</v>
       </c>
       <c r="B17" s="98" t="s">
-        <v>106</v>
+        <v>227</v>
       </c>
       <c r="C17" s="98"/>
       <c r="D17"/>
       <c r="E17" s="53" t="s">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="F17" s="53" t="s">
-        <v>107</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="202.5" customHeight="1">
@@ -6226,17 +7160,17 @@
         <v>16</v>
       </c>
       <c r="B18" s="98" t="s">
-        <v>108</v>
+        <v>229</v>
       </c>
       <c r="C18" s="98"/>
       <c r="D18" t="s">
-        <v>109</v>
+        <v>230</v>
       </c>
       <c r="E18" s="53" t="s">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="F18" s="53" t="s">
-        <v>110</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="327" customHeight="1">
@@ -6244,15 +7178,15 @@
         <v>17</v>
       </c>
       <c r="B19" s="98" t="s">
-        <v>111</v>
+        <v>232</v>
       </c>
       <c r="C19" s="98"/>
       <c r="D19"/>
       <c r="E19" s="53" t="s">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="F19" s="53" t="s">
-        <v>112</v>
+        <v>233</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="324" customHeight="1">
@@ -6260,15 +7194,15 @@
         <v>18</v>
       </c>
       <c r="B20" s="98" t="s">
-        <v>113</v>
+        <v>234</v>
       </c>
       <c r="C20" s="98"/>
       <c r="D20"/>
       <c r="E20" s="53" t="s">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="F20" s="53" t="s">
-        <v>114</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="275.25" customHeight="1">
@@ -6276,17 +7210,17 @@
         <v>19</v>
       </c>
       <c r="B21" s="98" t="s">
-        <v>115</v>
+        <v>236</v>
       </c>
       <c r="C21" s="98"/>
       <c r="D21" s="48" t="s">
-        <v>116</v>
+        <v>237</v>
       </c>
       <c r="E21" s="53" t="s">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="F21" s="53" t="s">
-        <v>117</v>
+        <v>238</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="381.75" customHeight="1">
@@ -6294,15 +7228,15 @@
         <v>20</v>
       </c>
       <c r="B22" s="98" t="s">
-        <v>118</v>
+        <v>239</v>
       </c>
       <c r="C22" s="98"/>
       <c r="D22" s="48"/>
       <c r="E22" s="53" t="s">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="F22" s="53" t="s">
-        <v>119</v>
+        <v>240</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="381.75" customHeight="1">
@@ -6310,15 +7244,15 @@
         <v>21</v>
       </c>
       <c r="B23" s="98" t="s">
-        <v>120</v>
+        <v>241</v>
       </c>
       <c r="C23" s="98"/>
       <c r="D23" s="48"/>
       <c r="E23" s="53" t="s">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="F23" s="53" t="s">
-        <v>121</v>
+        <v>242</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="134.25" customHeight="1">
@@ -6326,17 +7260,17 @@
         <v>22</v>
       </c>
       <c r="B24" s="102" t="s">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="C24" s="102"/>
       <c r="D24" s="48" t="s">
-        <v>123</v>
+        <v>244</v>
       </c>
       <c r="E24" s="53" t="s">
         <v>50</v>
       </c>
       <c r="F24" s="53" t="s">
-        <v>124</v>
+        <v>245</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="408" customHeight="1">
@@ -6344,12 +7278,12 @@
         <v>23</v>
       </c>
       <c r="B25" s="98" t="s">
-        <v>125</v>
+        <v>246</v>
       </c>
       <c r="C25" s="98"/>
       <c r="D25" s="48"/>
       <c r="E25" s="53" t="s">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="F25" s="53"/>
     </row>
@@ -6358,12 +7292,12 @@
         <v>24</v>
       </c>
       <c r="B26" s="98" t="s">
-        <v>126</v>
+        <v>247</v>
       </c>
       <c r="C26" s="98"/>
       <c r="D26" s="48"/>
       <c r="E26" s="53" t="s">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="F26" s="53"/>
     </row>
@@ -6372,17 +7306,17 @@
         <v>25</v>
       </c>
       <c r="B27" s="103" t="s">
-        <v>127</v>
+        <v>248</v>
       </c>
       <c r="C27" s="103"/>
       <c r="D27" s="48" t="s">
-        <v>128</v>
+        <v>249</v>
       </c>
       <c r="E27" s="53" t="s">
         <v>50</v>
       </c>
       <c r="F27" s="53" t="s">
-        <v>129</v>
+        <v>250</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="240" customHeight="1">
@@ -6390,15 +7324,15 @@
         <v>26</v>
       </c>
       <c r="B28" s="98" t="s">
-        <v>130</v>
+        <v>251</v>
       </c>
       <c r="C28" s="98"/>
       <c r="D28" s="48"/>
       <c r="E28" s="53" t="s">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="F28" s="53" t="s">
-        <v>131</v>
+        <v>252</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="213" customHeight="1">
@@ -6406,15 +7340,15 @@
         <v>27</v>
       </c>
       <c r="B29" s="98" t="s">
-        <v>132</v>
+        <v>253</v>
       </c>
       <c r="C29" s="98"/>
       <c r="D29" s="48"/>
       <c r="E29" s="53" t="s">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="F29" s="53" t="s">
-        <v>133</v>
+        <v>254</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="170.25" customHeight="1">
@@ -6422,17 +7356,17 @@
         <v>28</v>
       </c>
       <c r="B30" s="102" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="C30" s="102"/>
       <c r="D30" s="48" t="s">
-        <v>135</v>
+        <v>256</v>
       </c>
       <c r="E30" s="53" t="s">
         <v>50</v>
       </c>
       <c r="F30" s="53" t="s">
-        <v>136</v>
+        <v>257</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="229.5" customHeight="1">
@@ -6440,15 +7374,15 @@
         <v>29</v>
       </c>
       <c r="B31" s="98" t="s">
-        <v>137</v>
+        <v>258</v>
       </c>
       <c r="C31" s="98"/>
       <c r="D31" s="48"/>
       <c r="E31" s="53" t="s">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="F31" s="53" t="s">
-        <v>138</v>
+        <v>259</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="170.25" customHeight="1">
@@ -6456,15 +7390,15 @@
         <v>30</v>
       </c>
       <c r="B32" s="98" t="s">
-        <v>139</v>
+        <v>260</v>
       </c>
       <c r="C32" s="98"/>
       <c r="D32" s="48"/>
       <c r="E32" s="53" t="s">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="F32" s="53" t="s">
-        <v>140</v>
+        <v>261</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="182.25" customHeight="1">
@@ -6472,15 +7406,15 @@
         <v>31</v>
       </c>
       <c r="B33" s="98" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="C33" s="98"/>
       <c r="D33" s="48"/>
       <c r="E33" s="53" t="s">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="F33" s="53" t="s">
-        <v>142</v>
+        <v>263</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="186" customHeight="1">
@@ -6488,15 +7422,15 @@
         <v>32</v>
       </c>
       <c r="B34" s="102" t="s">
-        <v>143</v>
+        <v>264</v>
       </c>
       <c r="C34" s="102"/>
       <c r="D34" s="48"/>
       <c r="E34" s="53" t="s">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="F34" s="53" t="s">
-        <v>144</v>
+        <v>265</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="186" customHeight="1">
@@ -6504,17 +7438,17 @@
         <v>33</v>
       </c>
       <c r="B35" s="98" t="s">
-        <v>145</v>
+        <v>266</v>
       </c>
       <c r="C35" s="98"/>
       <c r="D35" s="48" t="s">
-        <v>146</v>
+        <v>267</v>
       </c>
       <c r="E35" s="53" t="s">
         <v>50</v>
       </c>
       <c r="F35" s="53" t="s">
-        <v>147</v>
+        <v>268</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="186" customHeight="1">
@@ -6522,17 +7456,17 @@
         <v>34</v>
       </c>
       <c r="B36" s="98" t="s">
-        <v>148</v>
+        <v>269</v>
       </c>
       <c r="C36" s="98"/>
       <c r="D36" s="48" t="s">
-        <v>149</v>
+        <v>270</v>
       </c>
       <c r="E36" s="53" t="s">
         <v>50</v>
       </c>
       <c r="F36" s="53" t="s">
-        <v>150</v>
+        <v>271</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="186" customHeight="1">
@@ -6540,17 +7474,17 @@
         <v>35</v>
       </c>
       <c r="B37" s="98" t="s">
-        <v>151</v>
+        <v>272</v>
       </c>
       <c r="C37" s="98"/>
       <c r="D37" s="48" t="s">
-        <v>99</v>
+        <v>220</v>
       </c>
       <c r="E37" s="53" t="s">
-        <v>152</v>
+        <v>273</v>
       </c>
       <c r="F37" s="53" t="s">
-        <v>153</v>
+        <v>274</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -6563,7 +7497,7 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="56" t="s">
-        <v>154</v>
+        <v>275</v>
       </c>
       <c r="B39" s="56"/>
       <c r="C39" s="56"/>
@@ -6573,7 +7507,7 @@
     </row>
     <row r="40" spans="1:6" ht="19.5" customHeight="1">
       <c r="A40" s="99" t="s">
-        <v>155</v>
+        <v>276</v>
       </c>
       <c r="B40" s="100"/>
       <c r="C40" s="100"/>
@@ -6589,7 +7523,7 @@
         <v>53</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>156</v>
+        <v>277</v>
       </c>
       <c r="D41" s="16" t="s">
         <v>54</v>
@@ -6598,7 +7532,7 @@
         <v>55</v>
       </c>
       <c r="F41" s="15" t="s">
-        <v>157</v>
+        <v>278</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="42.75" customHeight="1">
@@ -6609,16 +7543,16 @@
         <v>57</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>158</v>
+        <v>279</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>159</v>
+        <v>102</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>160</v>
+        <v>280</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>161</v>
+        <v>281</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="27" customHeight="1">
@@ -6629,16 +7563,16 @@
         <v>62</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>162</v>
+        <v>282</v>
       </c>
       <c r="D43" s="23" t="s">
         <v>58</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>163</v>
+        <v>283</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>73</v>
+        <v>194</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="24" customHeight="1">
@@ -6646,19 +7580,19 @@
         <v>10</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>165</v>
+        <v>284</v>
       </c>
       <c r="D44" s="23" t="s">
         <v>65</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>166</v>
+        <v>285</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>76</v>
+        <v>197</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="38.25" customHeight="1">
@@ -6666,19 +7600,19 @@
         <v>10</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>167</v>
+        <v>109</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>158</v>
+        <v>279</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>159</v>
+        <v>102</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>168</v>
+        <v>286</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>169</v>
+        <v>287</v>
       </c>
     </row>
     <row r="46" spans="1:6" s="58" customFormat="1" ht="124.5" customHeight="1">
@@ -6686,19 +7620,19 @@
         <v>10</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>170</v>
+        <v>288</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>165</v>
+        <v>284</v>
       </c>
       <c r="D46" s="23" t="s">
         <v>65</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>171</v>
+        <v>289</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>149</v>
+        <v>270</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="23.25" customHeight="1">
@@ -6706,19 +7640,19 @@
         <v>10</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>172</v>
+        <v>290</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>162</v>
+        <v>282</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>159</v>
+        <v>102</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>173</v>
+        <v>291</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>81</v>
+        <v>202</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -6726,19 +7660,19 @@
         <v>10</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>174</v>
+        <v>292</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>165</v>
+        <v>284</v>
       </c>
       <c r="D48" s="14" t="s">
         <v>65</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>175</v>
+        <v>293</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>84</v>
+        <v>205</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -6746,19 +7680,19 @@
         <v>10</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>176</v>
+        <v>294</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>165</v>
+        <v>284</v>
       </c>
       <c r="D49" s="14" t="s">
         <v>65</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>81</v>
+        <v>202</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -6766,19 +7700,19 @@
         <v>10</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>178</v>
+        <v>295</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>165</v>
+        <v>284</v>
       </c>
       <c r="D50" s="14" t="s">
         <v>65</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>179</v>
+        <v>296</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>86</v>
+        <v>207</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -6786,19 +7720,19 @@
         <v>10</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>180</v>
+        <v>297</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>165</v>
+        <v>284</v>
       </c>
       <c r="D51" s="14" t="s">
         <v>65</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>181</v>
+        <v>298</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>86</v>
+        <v>207</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -6806,19 +7740,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>182</v>
+        <v>299</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>165</v>
+        <v>284</v>
       </c>
       <c r="D52" s="14" t="s">
         <v>65</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>183</v>
+        <v>300</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>86</v>
+        <v>207</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -6826,19 +7760,19 @@
         <v>10</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>184</v>
+        <v>301</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>185</v>
+        <v>302</v>
       </c>
       <c r="D53" s="23" t="s">
         <v>65</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>186</v>
+        <v>303</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>88</v>
+        <v>209</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -6846,19 +7780,19 @@
         <v>10</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>187</v>
+        <v>304</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>185</v>
+        <v>302</v>
       </c>
       <c r="D54" s="23" t="s">
         <v>65</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>188</v>
+        <v>305</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>88</v>
+        <v>209</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -6866,19 +7800,19 @@
         <v>10</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>189</v>
+        <v>306</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>185</v>
+        <v>302</v>
       </c>
       <c r="D55" s="23" t="s">
         <v>65</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>190</v>
+        <v>307</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>99</v>
+        <v>220</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -6886,19 +7820,19 @@
         <v>10</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>191</v>
+        <v>308</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>192</v>
+        <v>309</v>
       </c>
       <c r="D56" s="23" t="s">
         <v>65</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>193</v>
+        <v>310</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>81</v>
+        <v>202</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -6906,19 +7840,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>194</v>
+        <v>311</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>195</v>
+        <v>312</v>
       </c>
       <c r="D57" s="23" t="s">
         <v>65</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>196</v>
+        <v>313</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>109</v>
+        <v>230</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -6926,19 +7860,19 @@
         <v>10</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>197</v>
+        <v>314</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>195</v>
+        <v>312</v>
       </c>
       <c r="D58" s="23" t="s">
         <v>65</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>198</v>
+        <v>315</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>116</v>
+        <v>237</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="95.25" customHeight="1">
@@ -6946,19 +7880,19 @@
         <v>10</v>
       </c>
       <c r="B59" s="14" t="s">
-        <v>199</v>
+        <v>316</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>200</v>
+        <v>317</v>
       </c>
       <c r="D59" s="23" t="s">
-        <v>159</v>
+        <v>102</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>201</v>
+        <v>318</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>202</v>
+        <v>319</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -6966,16 +7900,16 @@
         <v>10</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>203</v>
+        <v>320</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>200</v>
+        <v>317</v>
       </c>
       <c r="D60" s="23" t="s">
         <v>65</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>204</v>
+        <v>321</v>
       </c>
       <c r="F60" s="14"/>
     </row>
@@ -6984,19 +7918,19 @@
         <v>10</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>205</v>
+        <v>322</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>165</v>
+        <v>284</v>
       </c>
       <c r="D61" s="23" t="s">
         <v>65</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>206</v>
+        <v>323</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>135</v>
+        <v>256</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="108" customHeight="1">
@@ -7004,19 +7938,19 @@
         <v>10</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>207</v>
+        <v>324</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>200</v>
+        <v>317</v>
       </c>
       <c r="D62" s="23" t="s">
-        <v>208</v>
+        <v>325</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>209</v>
+        <v>326</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>210</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="105" customHeight="1">
@@ -7024,19 +7958,19 @@
         <v>10</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>211</v>
+        <v>328</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>200</v>
+        <v>317</v>
       </c>
       <c r="D63" s="23" t="s">
-        <v>208</v>
+        <v>325</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>212</v>
+        <v>329</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>210</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="111" customHeight="1">
@@ -7044,19 +7978,19 @@
         <v>10</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>213</v>
+        <v>330</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>200</v>
+        <v>317</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>208</v>
+        <v>325</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>214</v>
+        <v>331</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>210</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="99.75" customHeight="1">
@@ -7064,19 +7998,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>215</v>
+        <v>332</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>200</v>
+        <v>317</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>208</v>
+        <v>325</v>
       </c>
       <c r="E65" s="14" t="s">
-        <v>216</v>
+        <v>333</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>210</v>
+        <v>327</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="103.5" customHeight="1">
@@ -7084,19 +8018,19 @@
         <v>10</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>217</v>
+        <v>334</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>200</v>
+        <v>317</v>
       </c>
       <c r="D66" s="23" t="s">
-        <v>208</v>
+        <v>325</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>218</v>
+        <v>335</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>210</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="106.5" customHeight="1">
@@ -7104,19 +8038,19 @@
         <v>10</v>
       </c>
       <c r="B67" s="14" t="s">
-        <v>219</v>
+        <v>336</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>200</v>
+        <v>317</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>208</v>
+        <v>325</v>
       </c>
       <c r="E67" s="14" t="s">
-        <v>220</v>
+        <v>337</v>
       </c>
       <c r="F67" s="14" t="s">
-        <v>210</v>
+        <v>327</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="109.5" customHeight="1">
@@ -7124,19 +8058,19 @@
         <v>10</v>
       </c>
       <c r="B68" s="14" t="s">
-        <v>221</v>
+        <v>338</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>200</v>
+        <v>317</v>
       </c>
       <c r="D68" s="23" t="s">
         <v>65</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>222</v>
+        <v>339</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>210</v>
+        <v>327</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -7144,19 +8078,19 @@
         <v>10</v>
       </c>
       <c r="B69" s="14" t="s">
-        <v>223</v>
+        <v>340</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>165</v>
+        <v>284</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>208</v>
+        <v>325</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>224</v>
+        <v>341</v>
       </c>
       <c r="F69" s="14" t="s">
-        <v>146</v>
+        <v>267</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -7164,19 +8098,19 @@
         <v>10</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>225</v>
+        <v>342</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>200</v>
+        <v>317</v>
       </c>
       <c r="D70" s="14" t="s">
         <v>65</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>226</v>
+        <v>343</v>
       </c>
       <c r="F70" s="14" t="s">
-        <v>146</v>
+        <v>267</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -7184,19 +8118,19 @@
         <v>10</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>227</v>
+        <v>344</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>200</v>
+        <v>317</v>
       </c>
       <c r="D71" s="14" t="s">
         <v>65</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>228</v>
+        <v>345</v>
       </c>
       <c r="F71" s="14" t="s">
-        <v>146</v>
+        <v>267</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -7204,17 +8138,17 @@
         <v>10</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>229</v>
+        <v>346</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>230</v>
+        <v>347</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>231</v>
+        <v>348</v>
       </c>
       <c r="E72" s="14"/>
       <c r="F72" s="14" t="s">
-        <v>232</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -7262,1046 +8196,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59F34768-8776-4561-AACB-12FF947975B8}">
-  <dimension ref="A1:F53"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="17.140625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="55.28515625" style="26" customWidth="1"/>
-    <col min="3" max="3" width="24.85546875" style="26" customWidth="1"/>
-    <col min="4" max="4" width="36.7109375" style="26" customWidth="1"/>
-    <col min="5" max="5" width="46" style="26" customWidth="1"/>
-    <col min="6" max="6" width="32.85546875" style="26" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="26"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="15.75">
-      <c r="A1" s="93" t="s">
-        <v>233</v>
-      </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="25"/>
-    </row>
-    <row r="2" spans="1:6" ht="18.75" customHeight="1">
-      <c r="A2" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="F2" s="25"/>
-    </row>
-    <row r="3" spans="1:6" ht="30">
-      <c r="A3" s="27">
-        <v>1</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>235</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>236</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="28" t="s">
-        <v>237</v>
-      </c>
-      <c r="F3" s="25"/>
-    </row>
-    <row r="4" spans="1:6" ht="345">
-      <c r="A4" s="30">
-        <v>2</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>238</v>
-      </c>
-      <c r="C4" s="31" t="s">
-        <v>239</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" s="31" t="s">
-        <v>240</v>
-      </c>
-      <c r="F4" s="25"/>
-    </row>
-    <row r="5" spans="1:6" ht="210">
-      <c r="A5" s="30">
-        <v>3</v>
-      </c>
-      <c r="B5" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>242</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="31" t="s">
-        <v>243</v>
-      </c>
-      <c r="F5" s="25"/>
-    </row>
-    <row r="6" spans="1:6" ht="285">
-      <c r="A6" s="30">
-        <v>4</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>244</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>245</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="31" t="s">
-        <v>246</v>
-      </c>
-      <c r="F6" s="25"/>
-    </row>
-    <row r="7" spans="1:6" ht="300">
-      <c r="A7" s="30">
-        <v>5</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>247</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>248</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="31" t="s">
-        <v>249</v>
-      </c>
-      <c r="F7" s="25"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="25"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="33" t="s">
-        <v>250</v>
-      </c>
-      <c r="B9" s="33"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="95" t="s">
-        <v>251</v>
-      </c>
-      <c r="B10" s="96"/>
-      <c r="C10" s="96"/>
-      <c r="D10" s="96"/>
-      <c r="E10" s="97"/>
-      <c r="F10" s="17"/>
-    </row>
-    <row r="11" spans="1:6" ht="23.25" customHeight="1">
-      <c r="A11" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>252</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="29" t="s">
-        <v>255</v>
-      </c>
-      <c r="C12" s="29" t="s">
-        <v>256</v>
-      </c>
-      <c r="D12" s="34">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E12" s="35" t="s">
-        <v>257</v>
-      </c>
-      <c r="F12" s="29" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="32" t="s">
-        <v>259</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>260</v>
-      </c>
-      <c r="D13" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E13" s="37" t="s">
-        <v>261</v>
-      </c>
-      <c r="F13" s="32" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="32" t="s">
-        <v>262</v>
-      </c>
-      <c r="C14" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D14" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="E14" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="F14" s="32" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="32" t="s">
-        <v>265</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D15" s="34">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E15" s="30" t="s">
-        <v>266</v>
-      </c>
-      <c r="F15" s="32" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="32" t="s">
-        <v>268</v>
-      </c>
-      <c r="C16" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D16" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E16" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="F16" s="32" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="32" t="s">
-        <v>167</v>
-      </c>
-      <c r="C17" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D17" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="E17" s="32" t="s">
-        <v>270</v>
-      </c>
-      <c r="F17" s="32" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="32" t="s">
-        <v>271</v>
-      </c>
-      <c r="C18" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D18" s="34">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>272</v>
-      </c>
-      <c r="F18" s="32" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" s="32" t="s">
-        <v>273</v>
-      </c>
-      <c r="C19" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D19" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E19" s="30" t="s">
-        <v>274</v>
-      </c>
-      <c r="F19" s="32" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="32" t="s">
-        <v>275</v>
-      </c>
-      <c r="C20" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D20" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E20" s="30" t="s">
-        <v>276</v>
-      </c>
-      <c r="F20" s="32" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="C21" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D21" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E21" s="30" t="s">
-        <v>278</v>
-      </c>
-      <c r="F21" s="32" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="39" t="s">
-        <v>279</v>
-      </c>
-      <c r="C22" s="39" t="s">
-        <v>280</v>
-      </c>
-      <c r="D22" s="40">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E22" s="38" t="s">
-        <v>281</v>
-      </c>
-      <c r="F22" s="39" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" s="29" t="s">
-        <v>263</v>
-      </c>
-      <c r="D23" s="41">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E23" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="F23" s="29" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="C24" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="E24" s="32" t="s">
-        <v>283</v>
-      </c>
-      <c r="F24" s="32" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="32" t="s">
-        <v>284</v>
-      </c>
-      <c r="C25" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D25" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E25" s="30" t="s">
-        <v>285</v>
-      </c>
-      <c r="F25" s="32" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="32" t="s">
-        <v>286</v>
-      </c>
-      <c r="C26" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D26" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E26" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="F26" s="32" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" s="32" t="s">
-        <v>288</v>
-      </c>
-      <c r="C27" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D27" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E27" s="30" t="s">
-        <v>289</v>
-      </c>
-      <c r="F27" s="32" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" s="32" t="s">
-        <v>291</v>
-      </c>
-      <c r="C28" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D28" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E28" s="30" t="s">
-        <v>292</v>
-      </c>
-      <c r="F28" s="32" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="32" t="s">
-        <v>293</v>
-      </c>
-      <c r="C29" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D29" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E29" s="30" t="s">
-        <v>294</v>
-      </c>
-      <c r="F29" s="32" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="32" t="s">
-        <v>295</v>
-      </c>
-      <c r="C30" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D30" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E30" s="30" t="s">
-        <v>296</v>
-      </c>
-      <c r="F30" s="32" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31" s="32" t="s">
-        <v>297</v>
-      </c>
-      <c r="C31" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D31" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E31" s="30" t="s">
-        <v>298</v>
-      </c>
-      <c r="F31" s="32" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32" s="32" t="s">
-        <v>299</v>
-      </c>
-      <c r="C32" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D32" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E32" s="30" t="s">
-        <v>300</v>
-      </c>
-      <c r="F32" s="32" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" s="32" t="s">
-        <v>301</v>
-      </c>
-      <c r="C33" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D33" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E33" s="30" t="s">
-        <v>302</v>
-      </c>
-      <c r="F33" s="32" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="32" t="s">
-        <v>303</v>
-      </c>
-      <c r="C34" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D34" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E34" s="30" t="s">
-        <v>304</v>
-      </c>
-      <c r="F34" s="32" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B35" s="32" t="s">
-        <v>305</v>
-      </c>
-      <c r="C35" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D35" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E35" s="30" t="s">
-        <v>306</v>
-      </c>
-      <c r="F35" s="32" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B36" s="32" t="s">
-        <v>307</v>
-      </c>
-      <c r="C36" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D36" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E36" s="30" t="s">
-        <v>308</v>
-      </c>
-      <c r="F36" s="32" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B37" s="32" t="s">
-        <v>309</v>
-      </c>
-      <c r="C37" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D37" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E37" s="30" t="s">
-        <v>310</v>
-      </c>
-      <c r="F37" s="32" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B38" s="32" t="s">
-        <v>311</v>
-      </c>
-      <c r="C38" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D38" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E38" s="30" t="s">
-        <v>312</v>
-      </c>
-      <c r="F38" s="32" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B39" s="32" t="s">
-        <v>313</v>
-      </c>
-      <c r="C39" s="32" t="s">
-        <v>314</v>
-      </c>
-      <c r="D39" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E39" s="30" t="s">
-        <v>315</v>
-      </c>
-      <c r="F39" s="32" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B40" s="32" t="s">
-        <v>317</v>
-      </c>
-      <c r="C40" s="32" t="s">
-        <v>314</v>
-      </c>
-      <c r="D40" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E40" s="30" t="s">
-        <v>318</v>
-      </c>
-      <c r="F40" s="32" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B41" s="32" t="s">
-        <v>319</v>
-      </c>
-      <c r="C41" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D41" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E41" s="30" t="s">
-        <v>177</v>
-      </c>
-      <c r="F41" s="32" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B42" s="32" t="s">
-        <v>320</v>
-      </c>
-      <c r="C42" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D42" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E42" s="30" t="s">
-        <v>321</v>
-      </c>
-      <c r="F42" s="32" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B43" s="32" t="s">
-        <v>323</v>
-      </c>
-      <c r="C43" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D43" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E43" s="30" t="s">
-        <v>324</v>
-      </c>
-      <c r="F43" s="32" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B44" s="32" t="s">
-        <v>325</v>
-      </c>
-      <c r="C44" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D44" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E44" s="30" t="s">
-        <v>326</v>
-      </c>
-      <c r="F44" s="32" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B45" s="32" t="s">
-        <v>327</v>
-      </c>
-      <c r="C45" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D45" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="E45" s="32" t="s">
-        <v>328</v>
-      </c>
-      <c r="F45" s="32" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B46" s="32" t="s">
-        <v>330</v>
-      </c>
-      <c r="C46" s="32" t="s">
-        <v>314</v>
-      </c>
-      <c r="D46" s="34">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E46" s="30" t="s">
-        <v>331</v>
-      </c>
-      <c r="F46" s="32" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B47" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="C47" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D47" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E47" s="30" t="s">
-        <v>333</v>
-      </c>
-      <c r="F47" s="32" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B48" s="32" t="s">
-        <v>334</v>
-      </c>
-      <c r="C48" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D48" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E48" s="30" t="s">
-        <v>335</v>
-      </c>
-      <c r="F48" s="32" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B49" s="32" t="s">
-        <v>336</v>
-      </c>
-      <c r="C49" s="32" t="s">
-        <v>337</v>
-      </c>
-      <c r="D49" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E49" s="30" t="s">
-        <v>338</v>
-      </c>
-      <c r="F49" s="32" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B50" s="32" t="s">
-        <v>340</v>
-      </c>
-      <c r="C50" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D50" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E50" s="30" t="s">
-        <v>341</v>
-      </c>
-      <c r="F50" s="32" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B51" s="32" t="s">
-        <v>342</v>
-      </c>
-      <c r="C51" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D51" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E51" s="30" t="s">
-        <v>343</v>
-      </c>
-      <c r="F51" s="32" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B52" s="32" t="s">
-        <v>164</v>
-      </c>
-      <c r="C52" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D52" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E52" s="37" t="s">
-        <v>344</v>
-      </c>
-      <c r="F52" s="32" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B53" s="32" t="s">
-        <v>346</v>
-      </c>
-      <c r="C53" s="32" t="s">
-        <v>347</v>
-      </c>
-      <c r="D53" s="36">
-        <v>4.2361111111111113E-2</v>
-      </c>
-      <c r="E53" s="37" t="s">
-        <v>348</v>
-      </c>
-      <c r="F53" s="32" t="s">
-        <v>349</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -8473,7 +8368,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -8482,14 +8377,24 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED0C13A3-7E6E-461A-96D1-122E5E8A95BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F9B6A3B-BED9-4FC8-B2D5-053C860D1113}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F9B6A3B-BED9-4FC8-B2D5-053C860D1113}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFA63DCF-9520-4E04-9337-B32B74101E78}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFA63DCF-9520-4E04-9337-B32B74101E78}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED0C13A3-7E6E-461A-96D1-122E5E8A95BC}"/>
 </file>